--- a/data/数据收集 表2 画图用.xlsx
+++ b/data/数据收集 表2 画图用.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="89">
   <si>
     <t>序号</t>
   </si>
@@ -38,6 +38,9 @@
     <t>文献来源</t>
   </si>
   <si>
+    <t>拟合模型</t>
+  </si>
+  <si>
     <t>自旋值i</t>
   </si>
   <si>
@@ -83,6 +86,9 @@
     <t>Liu 2021</t>
   </si>
   <si>
+    <t>reflection</t>
+  </si>
+  <si>
     <t>Tripathi 2021</t>
   </si>
   <si>
@@ -92,6 +98,9 @@
     <t>Pahari 2018</t>
   </si>
   <si>
+    <t>continuum-fitting</t>
+  </si>
+  <si>
     <t>King 2014</t>
   </si>
   <si>
@@ -119,6 +128,9 @@
     <t>Morningstar 2014</t>
   </si>
   <si>
+    <t>combining</t>
+  </si>
+  <si>
     <t>Miller 2009</t>
   </si>
   <si>
@@ -203,30 +215,12 @@
     <t>XTE J1550-564</t>
   </si>
   <si>
-    <t>Kotrlová 2020</t>
-  </si>
-  <si>
-    <t>Šrámková 2015</t>
-  </si>
-  <si>
-    <t>Motta 2014</t>
-  </si>
-  <si>
-    <t>Mukhopadhyay 2009</t>
-  </si>
-  <si>
-    <t>Kato 2006</t>
-  </si>
-  <si>
     <t>Davis 2006</t>
   </si>
   <si>
     <t>MAXI J1820+070</t>
   </si>
   <si>
-    <t>Fiori 2025</t>
-  </si>
-  <si>
     <t>Fan 2024</t>
   </si>
   <si>
@@ -243,9 +237,6 @@
   </si>
   <si>
     <t>Guan 2021</t>
-  </si>
-  <si>
-    <t>Bhargava 2021</t>
   </si>
   <si>
     <t>Bharali 2019</t>
@@ -963,7 +954,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1041,9 +1032,6 @@
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1576,22 +1564,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:DK70"/>
+  <dimension ref="A1:DL63"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="9.02654867256637" style="3"/>
     <col min="2" max="2" width="29.5840707964602" style="4" customWidth="1"/>
     <col min="3" max="3" width="32.9203539823009" style="4" customWidth="1"/>
-    <col min="4" max="4" width="31.0088495575221" style="5" customWidth="1"/>
-    <col min="5" max="6" width="24.3451327433628" style="5" customWidth="1"/>
-    <col min="7" max="10" width="47.0973451327434" style="5" customWidth="1"/>
-    <col min="11" max="13" width="34.7787610619469" style="5" customWidth="1"/>
-    <col min="14" max="16" width="36.6371681415929" style="5" customWidth="1"/>
-    <col min="17" max="19" width="9.02654867256637" style="4"/>
-    <col min="20" max="115" width="9.02654867256637" style="6"/>
+    <col min="4" max="5" width="31.0088495575221" style="5" customWidth="1"/>
+    <col min="6" max="7" width="24.3451327433628" style="5" customWidth="1"/>
+    <col min="8" max="11" width="47.0973451327434" style="5" customWidth="1"/>
+    <col min="12" max="14" width="34.7787610619469" style="5" customWidth="1"/>
+    <col min="15" max="17" width="36.6371681415929" style="5" customWidth="1"/>
+    <col min="18" max="20" width="9.02654867256637" style="4"/>
+    <col min="21" max="116" width="9.02654867256637" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:115">
+    <row r="1" spans="1:116">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1640,60 +1628,65 @@
       <c r="P1" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:115">
+    <row r="2" s="1" customFormat="1" spans="1:116">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="10">
+        <v>18</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="10">
         <v>0.817</v>
-      </c>
-      <c r="E2" s="10">
-        <v>0.014</v>
       </c>
       <c r="F2" s="10">
         <v>0.014</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="10">
+        <v>0.014</v>
+      </c>
+      <c r="H2" s="11">
         <v>1.645</v>
-      </c>
-      <c r="H2" s="11">
-        <v>4</v>
       </c>
       <c r="I2" s="11">
         <v>4</v>
       </c>
       <c r="J2" s="11">
+        <v>4</v>
+      </c>
+      <c r="K2" s="11">
         <v>6</v>
       </c>
-      <c r="K2" s="11">
+      <c r="L2" s="11">
         <v>10.5</v>
-      </c>
-      <c r="L2" s="11">
-        <v>0.5</v>
       </c>
       <c r="M2" s="11">
         <v>0.5</v>
       </c>
       <c r="N2" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="O2" s="11">
         <v>10</v>
       </c>
-      <c r="O2" s="11">
-        <v>0</v>
-      </c>
       <c r="P2" s="11">
         <v>0</v>
       </c>
-      <c r="Q2" s="9"/>
+      <c r="Q2" s="11">
+        <v>0</v>
+      </c>
       <c r="R2" s="9"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="12"/>
+      <c r="T2" s="9"/>
       <c r="U2" s="12"/>
       <c r="V2" s="12"/>
       <c r="W2" s="12"/>
@@ -1789,58 +1782,61 @@
       <c r="DI2" s="12"/>
       <c r="DJ2" s="12"/>
       <c r="DK2" s="12"/>
+      <c r="DL2" s="12"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:115">
+    <row r="3" s="1" customFormat="1" spans="1:116">
       <c r="A3" s="3"/>
       <c r="B3" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="10">
+        <v>20</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="10">
         <v>0.99</v>
-      </c>
-      <c r="E3" s="10">
-        <v>0.003</v>
       </c>
       <c r="F3" s="10">
         <v>0.003</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="10">
+        <v>0.003</v>
+      </c>
+      <c r="H3" s="11">
         <v>1</v>
       </c>
-      <c r="H3" s="11">
+      <c r="I3" s="11">
         <v>8</v>
       </c>
-      <c r="I3" s="11">
+      <c r="J3" s="11">
         <v>4</v>
       </c>
-      <c r="J3" s="11">
+      <c r="K3" s="11">
         <v>6</v>
       </c>
-      <c r="K3" s="11">
+      <c r="L3" s="11">
         <v>10.5</v>
-      </c>
-      <c r="L3" s="11">
-        <v>0.5</v>
       </c>
       <c r="M3" s="11">
         <v>0.5</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="O3" s="10">
         <v>10</v>
       </c>
-      <c r="O3" s="10">
-        <v>0</v>
-      </c>
       <c r="P3" s="10">
         <v>0</v>
       </c>
-      <c r="Q3" s="9"/>
+      <c r="Q3" s="10">
+        <v>0</v>
+      </c>
       <c r="R3" s="9"/>
       <c r="S3" s="9"/>
-      <c r="T3" s="12"/>
+      <c r="T3" s="9"/>
       <c r="U3" s="12"/>
       <c r="V3" s="12"/>
       <c r="W3" s="12"/>
@@ -1936,58 +1932,61 @@
       <c r="DI3" s="12"/>
       <c r="DJ3" s="12"/>
       <c r="DK3" s="12"/>
+      <c r="DL3" s="12"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:115">
+    <row r="4" s="1" customFormat="1" spans="1:116">
       <c r="A4" s="3"/>
       <c r="B4" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="11">
+      <c r="E4" s="11">
         <v>0.85</v>
-      </c>
-      <c r="E4" s="10">
-        <v>0.07</v>
       </c>
       <c r="F4" s="10">
         <v>0.07</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
+        <v>0.07</v>
+      </c>
+      <c r="H4" s="11">
         <v>1.645</v>
       </c>
-      <c r="H4" s="11">
+      <c r="I4" s="11">
         <v>37</v>
       </c>
-      <c r="I4" s="11">
+      <c r="J4" s="11">
         <v>2</v>
       </c>
-      <c r="J4" s="11">
+      <c r="K4" s="11">
         <v>1</v>
       </c>
-      <c r="K4" s="11">
+      <c r="L4" s="11">
         <v>10.5</v>
-      </c>
-      <c r="L4" s="11">
-        <v>0.5</v>
       </c>
       <c r="M4" s="11">
         <v>0.5</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="O4" s="10">
         <v>10</v>
       </c>
-      <c r="O4" s="10">
-        <v>0</v>
-      </c>
       <c r="P4" s="10">
         <v>0</v>
       </c>
-      <c r="Q4" s="9"/>
+      <c r="Q4" s="10">
+        <v>0</v>
+      </c>
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
-      <c r="T4" s="12"/>
+      <c r="T4" s="9"/>
       <c r="U4" s="12"/>
       <c r="V4" s="12"/>
       <c r="W4" s="12"/>
@@ -2083,58 +2082,61 @@
       <c r="DI4" s="12"/>
       <c r="DJ4" s="12"/>
       <c r="DK4" s="12"/>
+      <c r="DL4" s="12"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:115">
+    <row r="5" s="1" customFormat="1" spans="1:116">
       <c r="A5" s="3"/>
       <c r="B5" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="11">
+        <v>22</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="11">
         <v>0.92</v>
-      </c>
-      <c r="E5" s="10">
-        <v>0.04</v>
       </c>
       <c r="F5" s="10">
         <v>0.04</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="H5" s="11">
         <v>3</v>
       </c>
-      <c r="H5" s="11">
+      <c r="I5" s="11">
         <v>64</v>
       </c>
-      <c r="I5" s="11">
-        <v>0</v>
-      </c>
       <c r="J5" s="11">
         <v>0</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="11">
+        <v>0</v>
+      </c>
+      <c r="L5" s="10">
         <v>10</v>
       </c>
-      <c r="L5" s="10">
-        <v>0</v>
-      </c>
       <c r="M5" s="10">
         <v>0</v>
       </c>
       <c r="N5" s="10">
+        <v>0</v>
+      </c>
+      <c r="O5" s="10">
         <v>10.1</v>
       </c>
-      <c r="O5" s="10">
-        <v>0</v>
-      </c>
       <c r="P5" s="10">
         <v>0</v>
       </c>
-      <c r="Q5" s="9"/>
+      <c r="Q5" s="10">
+        <v>0</v>
+      </c>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="12"/>
+      <c r="T5" s="9"/>
       <c r="U5" s="12"/>
       <c r="V5" s="12"/>
       <c r="W5" s="12"/>
@@ -2230,58 +2232,61 @@
       <c r="DI5" s="12"/>
       <c r="DJ5" s="12"/>
       <c r="DK5" s="12"/>
+      <c r="DL5" s="12"/>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:115">
+    <row r="6" s="1" customFormat="1" spans="1:116">
       <c r="A6" s="3"/>
       <c r="B6" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="11">
+        <v>24</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="11">
         <v>0.985</v>
       </c>
-      <c r="E6" s="10">
+      <c r="F6" s="10">
         <v>0.014</v>
       </c>
-      <c r="F6" s="10">
+      <c r="G6" s="10">
         <v>0.005</v>
       </c>
-      <c r="G6" s="11">
+      <c r="H6" s="11">
         <v>1</v>
       </c>
-      <c r="H6" s="11">
+      <c r="I6" s="11">
         <v>64</v>
       </c>
-      <c r="I6" s="11">
+      <c r="J6" s="11">
         <v>3</v>
       </c>
-      <c r="J6" s="11">
+      <c r="K6" s="11">
         <v>2</v>
       </c>
-      <c r="K6" s="11">
+      <c r="L6" s="11">
         <v>10</v>
       </c>
-      <c r="L6" s="11">
-        <v>0</v>
-      </c>
       <c r="M6" s="11">
         <v>0</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="11">
+        <v>0</v>
+      </c>
+      <c r="O6" s="10">
         <v>10</v>
       </c>
-      <c r="O6" s="10">
-        <v>0</v>
-      </c>
       <c r="P6" s="10">
         <v>0</v>
       </c>
-      <c r="Q6" s="9"/>
+      <c r="Q6" s="10">
+        <v>0</v>
+      </c>
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
-      <c r="T6" s="12"/>
+      <c r="T6" s="9"/>
       <c r="U6" s="12"/>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
@@ -2377,60 +2382,63 @@
       <c r="DI6" s="12"/>
       <c r="DJ6" s="12"/>
       <c r="DK6" s="12"/>
+      <c r="DL6" s="12"/>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:115">
+    <row r="7" s="1" customFormat="1" spans="1:116">
       <c r="A7" s="3">
         <v>2</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="10">
+        <v>26</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="10">
         <v>0.902</v>
       </c>
-      <c r="E7" s="10">
+      <c r="F7" s="10">
         <v>0.053</v>
       </c>
-      <c r="F7" s="10">
+      <c r="G7" s="10">
         <v>0.054</v>
       </c>
-      <c r="G7" s="11">
+      <c r="H7" s="11">
         <v>1.645</v>
       </c>
-      <c r="H7" s="11">
+      <c r="I7" s="11">
         <v>28.91</v>
       </c>
-      <c r="I7" s="11">
+      <c r="J7" s="11">
         <v>1.24</v>
       </c>
-      <c r="J7" s="11">
+      <c r="K7" s="11">
         <v>1.82</v>
       </c>
-      <c r="K7" s="11">
+      <c r="L7" s="11">
         <v>7.5</v>
-      </c>
-      <c r="L7" s="11">
-        <v>1</v>
       </c>
       <c r="M7" s="11">
         <v>1</v>
       </c>
       <c r="N7" s="11">
+        <v>1</v>
+      </c>
+      <c r="O7" s="11">
         <v>9.4</v>
-      </c>
-      <c r="O7" s="11">
-        <v>1</v>
       </c>
       <c r="P7" s="11">
         <v>1</v>
       </c>
-      <c r="Q7" s="9"/>
+      <c r="Q7" s="11">
+        <v>1</v>
+      </c>
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
-      <c r="T7" s="12"/>
+      <c r="T7" s="9"/>
       <c r="U7" s="12"/>
       <c r="V7" s="12"/>
       <c r="W7" s="12"/>
@@ -2526,58 +2534,61 @@
       <c r="DI7" s="12"/>
       <c r="DJ7" s="12"/>
       <c r="DK7" s="12"/>
+      <c r="DL7" s="12"/>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:115">
+    <row r="8" s="1" customFormat="1" spans="1:116">
       <c r="A8" s="3"/>
       <c r="B8" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="10">
+        <v>27</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="10">
         <v>0.959</v>
       </c>
-      <c r="E8" s="11">
+      <c r="F8" s="11">
         <v>0.039</v>
       </c>
-      <c r="F8" s="11">
+      <c r="G8" s="11">
         <v>0.031</v>
       </c>
-      <c r="G8" s="11">
+      <c r="H8" s="11">
         <v>1</v>
       </c>
-      <c r="H8" s="11">
+      <c r="I8" s="11">
         <v>67</v>
       </c>
-      <c r="I8" s="11">
+      <c r="J8" s="11">
         <v>8</v>
       </c>
-      <c r="J8" s="11">
+      <c r="K8" s="11">
         <v>7</v>
       </c>
-      <c r="K8" s="11">
+      <c r="L8" s="11">
         <v>7.5</v>
-      </c>
-      <c r="L8" s="11">
-        <v>1</v>
       </c>
       <c r="M8" s="11">
         <v>1</v>
       </c>
       <c r="N8" s="11">
+        <v>1</v>
+      </c>
+      <c r="O8" s="11">
         <v>9.4</v>
-      </c>
-      <c r="O8" s="11">
-        <v>2</v>
       </c>
       <c r="P8" s="11">
         <v>2</v>
       </c>
-      <c r="Q8" s="9"/>
+      <c r="Q8" s="11">
+        <v>2</v>
+      </c>
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
-      <c r="T8" s="12"/>
+      <c r="T8" s="9"/>
       <c r="U8" s="12"/>
       <c r="V8" s="12"/>
       <c r="W8" s="12"/>
@@ -2673,160 +2684,169 @@
       <c r="DI8" s="12"/>
       <c r="DJ8" s="12"/>
       <c r="DK8" s="12"/>
+      <c r="DL8" s="12"/>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:115">
+    <row r="9" s="2" customFormat="1" spans="1:116">
       <c r="A9" s="13"/>
       <c r="B9" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="11">
+        <v>28</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="11">
         <v>0.65</v>
       </c>
-      <c r="E9" s="11">
+      <c r="F9" s="11">
         <v>0.24</v>
       </c>
-      <c r="F9" s="11">
+      <c r="G9" s="11">
         <v>0.14</v>
       </c>
-      <c r="G9" s="11">
+      <c r="H9" s="11">
         <v>1</v>
       </c>
-      <c r="H9" s="11">
+      <c r="I9" s="11">
         <v>20.7</v>
-      </c>
-      <c r="I9" s="11">
-        <v>1.5</v>
       </c>
       <c r="J9" s="11">
         <v>1.5</v>
       </c>
       <c r="K9" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="L9" s="11">
         <v>7.5</v>
-      </c>
-      <c r="L9" s="11">
-        <v>0.5</v>
       </c>
       <c r="M9" s="11">
         <v>0.5</v>
       </c>
       <c r="N9" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="O9" s="11">
         <v>9.4</v>
-      </c>
-      <c r="O9" s="11">
-        <v>2</v>
       </c>
       <c r="P9" s="11">
         <v>2</v>
       </c>
-      <c r="Q9" s="15"/>
+      <c r="Q9" s="11">
+        <v>2</v>
+      </c>
       <c r="R9" s="15"/>
       <c r="S9" s="15"/>
+      <c r="T9" s="15"/>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:115">
+    <row r="10" s="2" customFormat="1" spans="1:116">
       <c r="A10" s="13"/>
       <c r="B10" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="11">
+        <v>29</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="11">
         <v>0.98</v>
       </c>
-      <c r="E10" s="11">
+      <c r="F10" s="11">
         <v>0.02</v>
       </c>
-      <c r="F10" s="11">
+      <c r="G10" s="11">
         <v>0.01</v>
       </c>
-      <c r="G10" s="11">
+      <c r="H10" s="11">
         <v>1</v>
       </c>
-      <c r="H10" s="11">
+      <c r="I10" s="11">
         <v>68</v>
       </c>
-      <c r="I10" s="11">
+      <c r="J10" s="11">
         <v>4</v>
       </c>
-      <c r="J10" s="11">
+      <c r="K10" s="11">
         <v>3</v>
       </c>
-      <c r="K10" s="11">
+      <c r="L10" s="11">
         <v>7.5</v>
-      </c>
-      <c r="L10" s="11">
-        <v>1</v>
       </c>
       <c r="M10" s="11">
         <v>1</v>
       </c>
       <c r="N10" s="11">
+        <v>1</v>
+      </c>
+      <c r="O10" s="11">
         <v>9.4</v>
-      </c>
-      <c r="O10" s="11">
-        <v>2</v>
       </c>
       <c r="P10" s="11">
         <v>2</v>
       </c>
-      <c r="Q10" s="15"/>
+      <c r="Q10" s="11">
+        <v>2</v>
+      </c>
       <c r="R10" s="15"/>
       <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:115">
+    <row r="11" s="1" customFormat="1" spans="1:116">
       <c r="A11" s="3"/>
       <c r="B11" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="10">
+        <v>30</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="10">
         <v>0.46</v>
-      </c>
-      <c r="E11" s="11">
-        <v>0.12</v>
       </c>
       <c r="F11" s="11">
         <v>0.12</v>
       </c>
       <c r="G11" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="H11" s="11">
         <v>1</v>
       </c>
-      <c r="H11" s="11">
+      <c r="I11" s="11">
         <v>36.3</v>
       </c>
-      <c r="I11" s="17">
-        <v>0</v>
-      </c>
       <c r="J11" s="17">
         <v>0</v>
       </c>
-      <c r="K11" s="11">
+      <c r="K11" s="17">
+        <v>0</v>
+      </c>
+      <c r="L11" s="11">
         <v>7.5</v>
       </c>
-      <c r="L11" s="11">
-        <v>0</v>
-      </c>
       <c r="M11" s="11">
         <v>0</v>
       </c>
       <c r="N11" s="11">
+        <v>0</v>
+      </c>
+      <c r="O11" s="11">
         <v>9.4</v>
       </c>
-      <c r="O11" s="11">
-        <v>0</v>
-      </c>
       <c r="P11" s="11">
         <v>0</v>
       </c>
-      <c r="Q11" s="9"/>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
       <c r="R11" s="9"/>
       <c r="S11" s="9"/>
-      <c r="T11" s="12"/>
+      <c r="T11" s="9"/>
       <c r="U11" s="12"/>
       <c r="V11" s="12"/>
       <c r="W11" s="12"/>
@@ -2922,58 +2942,61 @@
       <c r="DI11" s="12"/>
       <c r="DJ11" s="12"/>
       <c r="DK11" s="12"/>
+      <c r="DL11" s="12"/>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:115">
+    <row r="12" s="1" customFormat="1" spans="1:116">
       <c r="A12" s="3"/>
       <c r="B12" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="10">
+        <v>31</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="10">
         <v>0.67</v>
       </c>
-      <c r="E12" s="11">
+      <c r="F12" s="11">
         <v>0.08</v>
       </c>
-      <c r="F12" s="11">
+      <c r="G12" s="11">
         <v>0.15</v>
       </c>
-      <c r="G12" s="11">
+      <c r="H12" s="11">
         <v>1.645</v>
       </c>
-      <c r="H12" s="11">
+      <c r="I12" s="11">
         <v>36.3</v>
       </c>
-      <c r="I12" s="17">
+      <c r="J12" s="17">
         <v>3.4</v>
       </c>
-      <c r="J12" s="17">
+      <c r="K12" s="17">
         <v>5.3</v>
       </c>
-      <c r="K12" s="11">
+      <c r="L12" s="11">
         <v>7.5</v>
-      </c>
-      <c r="L12" s="11">
-        <v>1</v>
       </c>
       <c r="M12" s="11">
         <v>1</v>
       </c>
       <c r="N12" s="11">
+        <v>1</v>
+      </c>
+      <c r="O12" s="11">
         <v>9.4</v>
-      </c>
-      <c r="O12" s="11">
-        <v>1</v>
       </c>
       <c r="P12" s="11">
         <v>1</v>
       </c>
-      <c r="Q12" s="9"/>
+      <c r="Q12" s="11">
+        <v>1</v>
+      </c>
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
-      <c r="T12" s="12"/>
+      <c r="T12" s="9"/>
       <c r="U12" s="12"/>
       <c r="V12" s="12"/>
       <c r="W12" s="12"/>
@@ -3069,58 +3092,61 @@
       <c r="DI12" s="12"/>
       <c r="DJ12" s="12"/>
       <c r="DK12" s="12"/>
+      <c r="DL12" s="12"/>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:115">
+    <row r="13" s="1" customFormat="1" spans="1:116">
       <c r="A13" s="3"/>
       <c r="B13" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="10">
+        <v>32</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="10">
         <v>0.43</v>
       </c>
-      <c r="E13" s="11">
+      <c r="F13" s="11">
         <v>0.31</v>
       </c>
-      <c r="F13" s="11">
+      <c r="G13" s="11">
         <v>0.22</v>
       </c>
-      <c r="G13" s="11">
+      <c r="H13" s="11">
         <v>1.645</v>
       </c>
-      <c r="H13" s="11">
+      <c r="I13" s="11">
         <v>32</v>
       </c>
-      <c r="I13" s="11">
+      <c r="J13" s="11">
         <v>4</v>
       </c>
-      <c r="J13" s="11">
+      <c r="K13" s="11">
         <v>3</v>
       </c>
-      <c r="K13" s="11">
+      <c r="L13" s="11">
         <v>7.5</v>
-      </c>
-      <c r="L13" s="11">
-        <v>1</v>
       </c>
       <c r="M13" s="11">
         <v>1</v>
       </c>
       <c r="N13" s="11">
+        <v>1</v>
+      </c>
+      <c r="O13" s="11">
         <v>9.4</v>
-      </c>
-      <c r="O13" s="11">
-        <v>1</v>
       </c>
       <c r="P13" s="11">
         <v>1</v>
       </c>
-      <c r="Q13" s="9"/>
+      <c r="Q13" s="11">
+        <v>1</v>
+      </c>
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
-      <c r="T13" s="12"/>
+      <c r="T13" s="9"/>
       <c r="U13" s="12"/>
       <c r="V13" s="12"/>
       <c r="W13" s="12"/>
@@ -3216,58 +3242,61 @@
       <c r="DI13" s="12"/>
       <c r="DJ13" s="12"/>
       <c r="DK13" s="12"/>
+      <c r="DL13" s="12"/>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:115">
+    <row r="14" s="1" customFormat="1" spans="1:116">
       <c r="A14" s="3"/>
       <c r="B14" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="10">
+        <v>34</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="10">
         <v>0.3</v>
-      </c>
-      <c r="E14" s="11">
-        <v>0.1</v>
       </c>
       <c r="F14" s="11">
         <v>0.1</v>
       </c>
       <c r="G14" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="H14" s="11">
         <v>1</v>
       </c>
-      <c r="H14" s="11">
+      <c r="I14" s="11">
         <v>22</v>
       </c>
-      <c r="I14" s="11">
+      <c r="J14" s="11">
         <v>1</v>
       </c>
-      <c r="J14" s="11">
-        <v>0</v>
-      </c>
       <c r="K14" s="11">
+        <v>0</v>
+      </c>
+      <c r="L14" s="11">
         <v>8</v>
-      </c>
-      <c r="L14" s="11">
-        <v>1</v>
       </c>
       <c r="M14" s="11">
         <v>1</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="11">
+        <v>1</v>
+      </c>
+      <c r="O14" s="10">
         <v>9</v>
-      </c>
-      <c r="O14" s="10">
-        <v>2</v>
       </c>
       <c r="P14" s="10">
         <v>2</v>
       </c>
-      <c r="Q14" s="9"/>
+      <c r="Q14" s="10">
+        <v>2</v>
+      </c>
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
-      <c r="T14" s="12"/>
+      <c r="T14" s="9"/>
       <c r="U14" s="12"/>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
@@ -3363,58 +3392,61 @@
       <c r="DI14" s="12"/>
       <c r="DJ14" s="12"/>
       <c r="DK14" s="12"/>
+      <c r="DL14" s="12"/>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:115">
+    <row r="15" s="1" customFormat="1" spans="1:116">
       <c r="A15" s="3"/>
       <c r="B15" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="10">
+        <v>35</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="10">
         <v>0.8</v>
-      </c>
-      <c r="E15" s="10">
-        <v>0.05</v>
       </c>
       <c r="F15" s="10">
         <v>0.05</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="H15" s="11">
         <v>1</v>
       </c>
-      <c r="H15" s="11">
+      <c r="I15" s="11">
         <v>20.1167</v>
-      </c>
-      <c r="I15" s="11">
-        <v>1.0833</v>
       </c>
       <c r="J15" s="11">
         <v>1.0833</v>
       </c>
       <c r="K15" s="11">
+        <v>1.0833</v>
+      </c>
+      <c r="L15" s="11">
         <v>7.5</v>
       </c>
-      <c r="L15" s="10">
+      <c r="M15" s="10">
         <v>1</v>
       </c>
-      <c r="M15" s="11">
+      <c r="N15" s="11">
         <v>1</v>
       </c>
-      <c r="N15" s="10">
+      <c r="O15" s="10">
         <v>9.4</v>
-      </c>
-      <c r="O15" s="10">
-        <v>1</v>
       </c>
       <c r="P15" s="10">
         <v>1</v>
       </c>
-      <c r="Q15" s="9"/>
+      <c r="Q15" s="10">
+        <v>1</v>
+      </c>
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
-      <c r="T15" s="12"/>
+      <c r="T15" s="9"/>
       <c r="U15" s="12"/>
       <c r="V15" s="12"/>
       <c r="W15" s="12"/>
@@ -3510,60 +3542,63 @@
       <c r="DI15" s="12"/>
       <c r="DJ15" s="12"/>
       <c r="DK15" s="12"/>
+      <c r="DL15" s="12"/>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:115">
+    <row r="16" s="1" customFormat="1" spans="1:116">
       <c r="A16" s="3">
         <v>3</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="10">
+        <v>37</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="10">
         <v>0.77</v>
-      </c>
-      <c r="E16" s="10">
-        <v>0.22</v>
       </c>
       <c r="F16" s="10">
         <v>0.22</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="10">
+        <v>0.22</v>
+      </c>
+      <c r="H16" s="11">
         <v>1.645</v>
       </c>
-      <c r="H16" s="11">
+      <c r="I16" s="11">
         <v>65</v>
-      </c>
-      <c r="I16" s="11">
-        <v>5</v>
       </c>
       <c r="J16" s="11">
         <v>5</v>
       </c>
       <c r="K16" s="11">
+        <v>5</v>
+      </c>
+      <c r="L16" s="11">
         <v>6.5</v>
       </c>
-      <c r="L16" s="10">
+      <c r="M16" s="10">
         <v>2.5</v>
       </c>
-      <c r="M16" s="11">
+      <c r="N16" s="11">
         <v>2.5</v>
       </c>
-      <c r="N16" s="10">
+      <c r="O16" s="10">
         <v>3</v>
       </c>
-      <c r="O16" s="11">
-        <v>0</v>
-      </c>
       <c r="P16" s="11">
         <v>0</v>
       </c>
-      <c r="Q16" s="9"/>
+      <c r="Q16" s="11">
+        <v>0</v>
+      </c>
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
-      <c r="T16" s="12"/>
+      <c r="T16" s="9"/>
       <c r="U16" s="12"/>
       <c r="V16" s="12"/>
       <c r="W16" s="12"/>
@@ -3659,58 +3694,61 @@
       <c r="DI16" s="12"/>
       <c r="DJ16" s="12"/>
       <c r="DK16" s="12"/>
+      <c r="DL16" s="12"/>
     </row>
-    <row r="17" s="1" customFormat="1" spans="1:115">
+    <row r="17" s="1" customFormat="1" spans="1:116">
       <c r="A17" s="3"/>
       <c r="B17" s="8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="17">
+        <v>38</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="17">
         <v>0.976</v>
       </c>
-      <c r="E17" s="11">
-        <v>0</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="11">
+      <c r="F17" s="11">
+        <v>0</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="11">
         <v>1.645</v>
       </c>
-      <c r="H17" s="18">
+      <c r="I17" s="18">
         <v>65</v>
-      </c>
-      <c r="I17" s="18">
-        <v>5</v>
       </c>
       <c r="J17" s="18">
         <v>5</v>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="18">
+        <v>5</v>
+      </c>
+      <c r="L17" s="11">
         <v>8</v>
       </c>
-      <c r="L17" s="10">
+      <c r="M17" s="10">
         <v>1</v>
       </c>
-      <c r="M17" s="11">
+      <c r="N17" s="11">
         <v>1</v>
       </c>
-      <c r="N17" s="10">
+      <c r="O17" s="10">
         <v>3</v>
       </c>
-      <c r="O17" s="11">
-        <v>0</v>
-      </c>
       <c r="P17" s="11">
         <v>0</v>
       </c>
-      <c r="Q17" s="9"/>
+      <c r="Q17" s="11">
+        <v>0</v>
+      </c>
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
-      <c r="T17" s="12"/>
+      <c r="T17" s="9"/>
       <c r="U17" s="12"/>
       <c r="V17" s="12"/>
       <c r="W17" s="12"/>
@@ -3806,60 +3844,63 @@
       <c r="DI17" s="12"/>
       <c r="DJ17" s="12"/>
       <c r="DK17" s="12"/>
+      <c r="DL17" s="12"/>
     </row>
-    <row r="18" customFormat="1" spans="1:115">
+    <row r="18" customFormat="1" spans="1:116">
       <c r="A18" s="3">
         <v>4</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="20">
+        <v>41</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="20">
         <v>0.71</v>
       </c>
-      <c r="E18" s="10">
+      <c r="F18" s="10">
         <v>0.04</v>
       </c>
-      <c r="F18" s="10">
+      <c r="G18" s="10">
         <v>0.05</v>
       </c>
-      <c r="G18" s="11">
+      <c r="H18" s="11">
         <v>1.645</v>
       </c>
-      <c r="H18" s="21">
+      <c r="I18" s="21">
         <v>32</v>
-      </c>
-      <c r="I18" s="11">
-        <v>2</v>
       </c>
       <c r="J18" s="11">
         <v>2</v>
       </c>
       <c r="K18" s="11">
+        <v>2</v>
+      </c>
+      <c r="L18" s="11">
         <v>11.5</v>
       </c>
-      <c r="L18" s="11">
+      <c r="M18" s="11">
         <v>0.8</v>
       </c>
-      <c r="M18" s="21">
+      <c r="N18" s="21">
         <v>0.5</v>
       </c>
-      <c r="N18" s="21">
+      <c r="O18" s="21">
         <v>12.5</v>
       </c>
-      <c r="O18" s="21">
+      <c r="P18" s="21">
         <v>0.3</v>
       </c>
-      <c r="P18" s="21">
+      <c r="Q18" s="21">
         <v>1</v>
       </c>
-      <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
-      <c r="T18" s="6"/>
+      <c r="T18" s="4"/>
       <c r="U18" s="6"/>
       <c r="V18" s="6"/>
       <c r="W18" s="6"/>
@@ -3955,32 +3996,33 @@
       <c r="DI18" s="6"/>
       <c r="DJ18" s="6"/>
       <c r="DK18" s="6"/>
+      <c r="DL18" s="6"/>
     </row>
-    <row r="19" customFormat="1" spans="1:115">
+    <row r="19" customFormat="1" spans="1:116">
       <c r="A19" s="3"/>
       <c r="B19" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="20">
+        <v>42</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="20">
         <v>0.8</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F19" s="10">
-        <v>0</v>
-      </c>
-      <c r="G19" s="11">
+      <c r="F19" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="10">
+        <v>0</v>
+      </c>
+      <c r="H19" s="11">
         <v>1.645</v>
       </c>
-      <c r="H19" s="11">
+      <c r="I19" s="11">
         <v>50</v>
-      </c>
-      <c r="I19" s="11">
-        <v>10</v>
       </c>
       <c r="J19" s="11">
         <v>10</v>
@@ -3989,24 +4031,26 @@
         <v>10</v>
       </c>
       <c r="L19" s="11">
+        <v>10</v>
+      </c>
+      <c r="M19" s="11">
         <v>2</v>
       </c>
-      <c r="M19" s="21">
+      <c r="N19" s="21">
         <v>2</v>
       </c>
-      <c r="N19" s="21">
+      <c r="O19" s="21">
         <v>7.5</v>
-      </c>
-      <c r="O19" s="21">
-        <v>3.5</v>
       </c>
       <c r="P19" s="21">
         <v>3.5</v>
       </c>
-      <c r="Q19" s="4"/>
+      <c r="Q19" s="21">
+        <v>3.5</v>
+      </c>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
-      <c r="T19" s="6"/>
+      <c r="T19" s="4"/>
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
       <c r="W19" s="6"/>
@@ -4102,58 +4146,61 @@
       <c r="DI19" s="6"/>
       <c r="DJ19" s="6"/>
       <c r="DK19" s="6"/>
+      <c r="DL19" s="6"/>
     </row>
-    <row r="20" customFormat="1" spans="1:115">
+    <row r="20" customFormat="1" spans="1:116">
       <c r="A20" s="3"/>
       <c r="B20" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="20">
+        <v>43</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="20">
         <v>0.95</v>
       </c>
-      <c r="E20" s="10">
+      <c r="F20" s="10">
         <v>0.05</v>
       </c>
-      <c r="F20" s="10">
+      <c r="G20" s="10">
         <v>0.03</v>
       </c>
-      <c r="G20" s="11">
+      <c r="H20" s="11">
         <v>1.645</v>
       </c>
-      <c r="H20" s="11">
+      <c r="I20" s="11">
         <v>48</v>
-      </c>
-      <c r="I20" s="11">
-        <v>1</v>
       </c>
       <c r="J20" s="11">
         <v>1</v>
       </c>
       <c r="K20" s="11">
+        <v>1</v>
+      </c>
+      <c r="L20" s="11">
         <v>8</v>
       </c>
-      <c r="L20" s="11">
-        <v>0</v>
-      </c>
-      <c r="M20" s="21">
+      <c r="M20" s="11">
         <v>0</v>
       </c>
       <c r="N20" s="21">
+        <v>0</v>
+      </c>
+      <c r="O20" s="21">
         <v>10</v>
       </c>
-      <c r="O20" s="21">
-        <v>0</v>
-      </c>
       <c r="P20" s="21">
         <v>0</v>
       </c>
-      <c r="Q20" s="4"/>
+      <c r="Q20" s="21">
+        <v>0</v>
+      </c>
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
-      <c r="T20" s="6"/>
+      <c r="T20" s="4"/>
       <c r="U20" s="6"/>
       <c r="V20" s="6"/>
       <c r="W20" s="6"/>
@@ -4249,58 +4296,61 @@
       <c r="DI20" s="6"/>
       <c r="DJ20" s="6"/>
       <c r="DK20" s="6"/>
+      <c r="DL20" s="6"/>
     </row>
-    <row r="21" s="1" customFormat="1" spans="1:115">
+    <row r="21" s="1" customFormat="1" spans="1:116">
       <c r="A21" s="3"/>
       <c r="B21" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="10">
+        <v>0.97</v>
+      </c>
+      <c r="F21" s="10">
+        <v>0</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="11">
+        <v>1.645</v>
+      </c>
+      <c r="I21" s="11">
         <v>36</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="10">
-        <v>0.97</v>
-      </c>
-      <c r="E21" s="10">
-        <v>0</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="11">
-        <v>1.645</v>
-      </c>
-      <c r="H21" s="11">
-        <v>36</v>
-      </c>
-      <c r="I21" s="11">
-        <v>4</v>
       </c>
       <c r="J21" s="11">
         <v>4</v>
       </c>
       <c r="K21" s="11">
+        <v>4</v>
+      </c>
+      <c r="L21" s="11">
         <v>8</v>
       </c>
-      <c r="L21" s="11">
-        <v>0</v>
-      </c>
-      <c r="M21" s="21">
+      <c r="M21" s="11">
         <v>0</v>
       </c>
       <c r="N21" s="21">
+        <v>0</v>
+      </c>
+      <c r="O21" s="21">
         <v>5.8</v>
-      </c>
-      <c r="O21" s="21">
-        <v>0.5</v>
       </c>
       <c r="P21" s="21">
         <v>0.5</v>
       </c>
-      <c r="Q21" s="9"/>
+      <c r="Q21" s="21">
+        <v>0.5</v>
+      </c>
       <c r="R21" s="9"/>
       <c r="S21" s="9"/>
-      <c r="T21" s="12"/>
+      <c r="T21" s="9"/>
       <c r="U21" s="12"/>
       <c r="V21" s="12"/>
       <c r="W21" s="12"/>
@@ -4396,58 +4446,61 @@
       <c r="DI21" s="12"/>
       <c r="DJ21" s="12"/>
       <c r="DK21" s="12"/>
+      <c r="DL21" s="12"/>
     </row>
-    <row r="22" customFormat="1" spans="1:115">
+    <row r="22" customFormat="1" spans="1:116">
       <c r="A22" s="3"/>
       <c r="B22" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="20">
+        <v>45</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="20">
         <v>0.4</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="F22" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="10">
+        <v>0</v>
+      </c>
+      <c r="H22" s="11">
+        <v>1</v>
+      </c>
+      <c r="I22" s="20">
         <v>35</v>
-      </c>
-      <c r="F22" s="10">
-        <v>0</v>
-      </c>
-      <c r="G22" s="11">
-        <v>1</v>
-      </c>
-      <c r="H22" s="20">
-        <v>35</v>
-      </c>
-      <c r="I22" s="11">
-        <v>10</v>
       </c>
       <c r="J22" s="11">
         <v>10</v>
       </c>
       <c r="K22" s="11">
+        <v>10</v>
+      </c>
+      <c r="L22" s="11">
         <v>8</v>
       </c>
-      <c r="L22" s="11">
-        <v>0</v>
-      </c>
-      <c r="M22" s="21">
+      <c r="M22" s="11">
         <v>0</v>
       </c>
       <c r="N22" s="21">
+        <v>0</v>
+      </c>
+      <c r="O22" s="21">
         <v>7</v>
       </c>
-      <c r="O22" s="21">
-        <v>0</v>
-      </c>
       <c r="P22" s="21">
         <v>0</v>
       </c>
-      <c r="Q22" s="4"/>
+      <c r="Q22" s="21">
+        <v>0</v>
+      </c>
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
-      <c r="T22" s="6"/>
+      <c r="T22" s="4"/>
       <c r="U22" s="6"/>
       <c r="V22" s="6"/>
       <c r="W22" s="6"/>
@@ -4543,58 +4596,61 @@
       <c r="DI22" s="6"/>
       <c r="DJ22" s="6"/>
       <c r="DK22" s="6"/>
+      <c r="DL22" s="6"/>
     </row>
-    <row r="23" customFormat="1" spans="1:115">
+    <row r="23" customFormat="1" spans="1:116">
       <c r="A23" s="3"/>
       <c r="B23" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="20">
+        <v>46</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="20">
         <v>0.89</v>
-      </c>
-      <c r="E23" s="20">
-        <v>0.04</v>
       </c>
       <c r="F23" s="20">
         <v>0.04</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="20">
+        <v>0.04</v>
+      </c>
+      <c r="H23" s="11">
         <v>1</v>
       </c>
-      <c r="H23" s="20">
+      <c r="I23" s="20">
         <v>18.5</v>
-      </c>
-      <c r="I23" s="20">
-        <v>0.5</v>
       </c>
       <c r="J23" s="20">
         <v>0.5</v>
       </c>
-      <c r="K23" s="11">
+      <c r="K23" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="L23" s="11">
         <v>8</v>
       </c>
-      <c r="L23" s="11">
-        <v>0</v>
-      </c>
       <c r="M23" s="11">
         <v>0</v>
       </c>
-      <c r="N23" s="10">
+      <c r="N23" s="11">
+        <v>0</v>
+      </c>
+      <c r="O23" s="10">
         <v>5.8</v>
       </c>
-      <c r="O23" s="11">
-        <v>0</v>
-      </c>
-      <c r="P23" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q23" s="4"/>
+      <c r="P23" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
-      <c r="T23" s="6"/>
+      <c r="T23" s="4"/>
       <c r="U23" s="6"/>
       <c r="V23" s="6"/>
       <c r="W23" s="6"/>
@@ -4690,276 +4746,291 @@
       <c r="DI23" s="6"/>
       <c r="DJ23" s="6"/>
       <c r="DK23" s="6"/>
+      <c r="DL23" s="6"/>
     </row>
-    <row r="24" spans="1:115">
+    <row r="24" spans="1:116">
       <c r="A24" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="20">
+        <v>48</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="20">
         <v>0.85</v>
       </c>
-      <c r="E24" s="11">
+      <c r="F24" s="11">
         <v>0.05</v>
       </c>
-      <c r="F24" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G24" s="11">
+      <c r="G24" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="11">
         <v>1</v>
       </c>
-      <c r="H24" s="11">
+      <c r="I24" s="11">
         <v>11</v>
       </c>
-      <c r="I24" s="11">
+      <c r="J24" s="11">
         <v>0.1</v>
       </c>
-      <c r="J24" s="11">
+      <c r="K24" s="11">
         <v>5</v>
       </c>
-      <c r="K24" s="11">
+      <c r="L24" s="11">
         <v>8</v>
       </c>
-      <c r="L24" s="11">
-        <v>0</v>
-      </c>
       <c r="M24" s="11">
         <v>0</v>
       </c>
-      <c r="N24" s="10">
+      <c r="N24" s="11">
+        <v>0</v>
+      </c>
+      <c r="O24" s="10">
         <v>5.8</v>
       </c>
-      <c r="O24" s="11">
-        <v>0</v>
-      </c>
-      <c r="P24" s="10" t="s">
-        <v>35</v>
+      <c r="P24" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="10" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:115">
+    <row r="25" spans="1:116">
       <c r="A25" s="3">
         <v>5</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="20">
+        <v>29</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="20">
         <v>0.98</v>
       </c>
-      <c r="E25" s="20">
+      <c r="F25" s="20">
         <v>0.02</v>
       </c>
-      <c r="F25" s="20">
+      <c r="G25" s="20">
         <v>0.01</v>
       </c>
-      <c r="G25" s="11">
+      <c r="H25" s="11">
         <v>1</v>
       </c>
-      <c r="H25" s="23">
+      <c r="I25" s="23">
         <v>56</v>
-      </c>
-      <c r="I25" s="23">
-        <v>4</v>
       </c>
       <c r="J25" s="23">
         <v>4</v>
       </c>
       <c r="K25" s="23">
+        <v>4</v>
+      </c>
+      <c r="L25" s="23">
         <v>8.5</v>
-      </c>
-      <c r="L25" s="23">
-        <v>0.8</v>
       </c>
       <c r="M25" s="23">
         <v>0.8</v>
       </c>
       <c r="N25" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="O25" s="23">
         <v>11.21</v>
       </c>
-      <c r="O25" s="23">
+      <c r="P25" s="23">
         <v>1.96</v>
       </c>
-      <c r="P25" s="23">
+      <c r="Q25" s="23">
         <v>1.65</v>
       </c>
-      <c r="Q25" s="24"/>
       <c r="R25" s="24"/>
       <c r="S25" s="24"/>
       <c r="T25" s="24"/>
       <c r="U25" s="24"/>
       <c r="V25" s="24"/>
+      <c r="W25" s="24"/>
     </row>
-    <row r="26" spans="1:115">
+    <row r="26" spans="1:116">
       <c r="B26" s="22" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="20">
+        <v>50</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="20">
         <v>0.2</v>
-      </c>
-      <c r="E26" s="20">
-        <v>0.3</v>
       </c>
       <c r="F26" s="20">
         <v>0.3</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="H26" s="11">
         <v>1</v>
       </c>
-      <c r="H26" s="23">
+      <c r="I26" s="23">
         <v>75</v>
-      </c>
-      <c r="I26" s="23">
-        <v>3</v>
       </c>
       <c r="J26" s="23">
         <v>3</v>
       </c>
       <c r="K26" s="23">
+        <v>3</v>
+      </c>
+      <c r="L26" s="23">
         <v>8.5</v>
-      </c>
-      <c r="L26" s="23">
-        <v>0.8</v>
       </c>
       <c r="M26" s="23">
         <v>0.8</v>
       </c>
       <c r="N26" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="O26" s="23">
         <v>11.21</v>
       </c>
-      <c r="O26" s="23">
+      <c r="P26" s="23">
         <v>1.96</v>
       </c>
-      <c r="P26" s="23">
+      <c r="Q26" s="23">
         <v>1.65</v>
       </c>
-      <c r="Q26" s="24"/>
       <c r="R26" s="24"/>
       <c r="S26" s="24"/>
       <c r="T26" s="24"/>
       <c r="U26" s="24"/>
       <c r="V26" s="24"/>
+      <c r="W26" s="24"/>
     </row>
-    <row r="27" spans="1:115">
+    <row r="27" spans="1:116">
       <c r="A27" s="3">
         <v>6</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="5">
+        <v>52</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="5">
         <v>0.88</v>
       </c>
-      <c r="E27" s="20">
+      <c r="F27" s="20">
         <v>0.02</v>
       </c>
-      <c r="F27" s="20">
+      <c r="G27" s="20">
         <v>0.01</v>
       </c>
-      <c r="G27" s="11">
+      <c r="H27" s="11">
         <v>1.645</v>
       </c>
-      <c r="H27" s="23">
+      <c r="I27" s="23">
         <v>63.7</v>
       </c>
-      <c r="I27" s="23">
+      <c r="J27" s="23">
         <v>1</v>
       </c>
-      <c r="J27" s="23">
+      <c r="K27" s="23">
         <v>1.3</v>
       </c>
-      <c r="K27" s="23">
+      <c r="L27" s="23">
         <v>10.81</v>
-      </c>
-      <c r="L27" s="23">
-        <v>3.52</v>
       </c>
       <c r="M27" s="23">
         <v>3.52</v>
       </c>
       <c r="N27" s="23">
+        <v>3.52</v>
+      </c>
+      <c r="O27" s="23">
         <v>5.8</v>
-      </c>
-      <c r="O27" s="23">
-        <v>0.3</v>
       </c>
       <c r="P27" s="23">
         <v>0.3</v>
       </c>
-      <c r="Q27" s="24"/>
+      <c r="Q27" s="23">
+        <v>0.3</v>
+      </c>
       <c r="R27" s="24"/>
       <c r="S27" s="24"/>
       <c r="T27" s="24"/>
       <c r="U27" s="24"/>
       <c r="V27" s="24"/>
+      <c r="W27" s="24"/>
     </row>
-    <row r="28" s="1" customFormat="1" spans="1:115">
+    <row r="28" s="1" customFormat="1" spans="1:116">
       <c r="A28" s="3"/>
       <c r="B28" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="10">
+        <v>53</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="10">
         <v>0.85</v>
-      </c>
-      <c r="E28" s="10">
-        <v>0.03</v>
       </c>
       <c r="F28" s="10">
         <v>0.03</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="H28" s="11">
         <v>1.645</v>
       </c>
-      <c r="H28" s="23">
+      <c r="I28" s="23">
         <v>53</v>
-      </c>
-      <c r="I28" s="23">
-        <v>0.5</v>
       </c>
       <c r="J28" s="23">
         <v>0.5</v>
       </c>
       <c r="K28" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="L28" s="23">
         <v>10.81</v>
-      </c>
-      <c r="L28" s="23">
-        <v>3.52</v>
       </c>
       <c r="M28" s="23">
         <v>3.52</v>
       </c>
       <c r="N28" s="23">
+        <v>3.52</v>
+      </c>
+      <c r="O28" s="23">
         <v>5.5</v>
-      </c>
-      <c r="O28" s="23">
-        <v>3.6</v>
       </c>
       <c r="P28" s="23">
         <v>3.6</v>
       </c>
-      <c r="Q28" s="24"/>
+      <c r="Q28" s="23">
+        <v>3.6</v>
+      </c>
       <c r="R28" s="24"/>
       <c r="S28" s="24"/>
       <c r="T28" s="24"/>
       <c r="U28" s="24"/>
       <c r="V28" s="24"/>
-      <c r="W28" s="12"/>
+      <c r="W28" s="24"/>
       <c r="X28" s="12"/>
       <c r="Y28" s="12"/>
       <c r="Z28" s="12"/>
@@ -5052,29 +5123,30 @@
       <c r="DI28" s="12"/>
       <c r="DJ28" s="12"/>
       <c r="DK28" s="12"/>
+      <c r="DL28" s="12"/>
     </row>
-    <row r="29" s="1" customFormat="1" spans="1:115">
+    <row r="29" s="1" customFormat="1" spans="1:116">
       <c r="A29" s="3"/>
       <c r="B29" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="10">
+        <v>54</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="10">
         <v>0.8</v>
       </c>
-      <c r="E29" s="11">
-        <v>0</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G29" s="11">
+      <c r="F29" s="11">
+        <v>0</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H29" s="11">
         <v>1.645</v>
-      </c>
-      <c r="H29" s="23">
-        <v>42</v>
       </c>
       <c r="I29" s="23">
         <v>42</v>
@@ -5083,27 +5155,29 @@
         <v>42</v>
       </c>
       <c r="K29" s="23">
+        <v>42</v>
+      </c>
+      <c r="L29" s="23">
         <v>10.81</v>
-      </c>
-      <c r="L29" s="23">
-        <v>3.52</v>
       </c>
       <c r="M29" s="23">
         <v>3.52</v>
       </c>
-      <c r="N29" s="11">
+      <c r="N29" s="23">
+        <v>3.52</v>
+      </c>
+      <c r="O29" s="11">
         <v>5.2</v>
-      </c>
-      <c r="O29" s="11">
-        <v>4.5</v>
       </c>
       <c r="P29" s="11">
         <v>4.5</v>
       </c>
-      <c r="Q29" s="9"/>
+      <c r="Q29" s="11">
+        <v>4.5</v>
+      </c>
       <c r="R29" s="9"/>
       <c r="S29" s="9"/>
-      <c r="T29" s="12"/>
+      <c r="T29" s="9"/>
       <c r="U29" s="12"/>
       <c r="V29" s="12"/>
       <c r="W29" s="12"/>
@@ -5199,57 +5273,60 @@
       <c r="DI29" s="12"/>
       <c r="DJ29" s="12"/>
       <c r="DK29" s="12"/>
+      <c r="DL29" s="12"/>
     </row>
-    <row r="30" spans="1:115">
+    <row r="30" spans="1:116">
       <c r="A30" s="3">
         <v>7</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="20">
+        <v>56</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="20">
         <v>0.863</v>
       </c>
-      <c r="E30" s="20">
+      <c r="F30" s="20">
         <v>0.015</v>
       </c>
-      <c r="F30" s="20">
+      <c r="G30" s="20">
         <v>0.014</v>
       </c>
-      <c r="G30" s="25">
+      <c r="H30" s="25">
         <v>2.576</v>
       </c>
-      <c r="H30" s="23">
+      <c r="I30" s="23">
         <v>60</v>
       </c>
-      <c r="I30" s="20">
-        <v>0</v>
-      </c>
       <c r="J30" s="20">
         <v>0</v>
       </c>
-      <c r="K30" s="23">
+      <c r="K30" s="20">
+        <v>0</v>
+      </c>
+      <c r="L30" s="23">
         <v>8.6</v>
       </c>
-      <c r="L30" s="23">
-        <v>0</v>
-      </c>
       <c r="M30" s="23">
         <v>0</v>
       </c>
       <c r="N30" s="23">
+        <v>0</v>
+      </c>
+      <c r="O30" s="23">
         <v>12.4</v>
       </c>
-      <c r="O30" s="23">
-        <v>0</v>
-      </c>
       <c r="P30" s="23">
         <v>0</v>
       </c>
-      <c r="Q30" s="24"/>
+      <c r="Q30" s="23">
+        <v>0</v>
+      </c>
       <c r="R30" s="24"/>
       <c r="S30" s="24"/>
       <c r="T30" s="24"/>
@@ -5261,54 +5338,57 @@
       <c r="Z30" s="24"/>
       <c r="AA30" s="24"/>
       <c r="AB30" s="24"/>
+      <c r="AC30" s="24"/>
     </row>
-    <row r="31" spans="1:115">
+    <row r="31" spans="1:116">
       <c r="B31" s="22" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D31" s="20">
+        <v>57</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="20">
         <v>0.98</v>
-      </c>
-      <c r="E31" s="20">
-        <v>0.01</v>
       </c>
       <c r="F31" s="20">
         <v>0.01</v>
       </c>
       <c r="G31" s="20">
+        <v>0.01</v>
+      </c>
+      <c r="H31" s="20">
         <v>999999</v>
       </c>
-      <c r="H31" s="20">
+      <c r="I31" s="20">
         <v>72</v>
-      </c>
-      <c r="I31" s="20">
-        <v>1</v>
       </c>
       <c r="J31" s="20">
         <v>1</v>
       </c>
-      <c r="K31" s="23">
+      <c r="K31" s="20">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
         <v>11</v>
       </c>
-      <c r="L31" s="23">
-        <v>0</v>
-      </c>
       <c r="M31" s="23">
         <v>0</v>
       </c>
       <c r="N31" s="23">
+        <v>0</v>
+      </c>
+      <c r="O31" s="23">
         <v>10.1</v>
-      </c>
-      <c r="O31" s="23">
-        <v>0.6</v>
       </c>
       <c r="P31" s="23">
         <v>0.6</v>
       </c>
-      <c r="Q31" s="24"/>
+      <c r="Q31" s="23">
+        <v>0.6</v>
+      </c>
       <c r="R31" s="24"/>
       <c r="S31" s="24"/>
       <c r="T31" s="24"/>
@@ -5320,54 +5400,57 @@
       <c r="Z31" s="24"/>
       <c r="AA31" s="24"/>
       <c r="AB31" s="24"/>
+      <c r="AC31" s="24"/>
     </row>
-    <row r="32" spans="1:115">
+    <row r="32" spans="1:116">
       <c r="B32" s="22" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="D32" s="23">
+        <v>58</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="23">
         <v>0.98</v>
-      </c>
-      <c r="E32" s="20">
-        <v>0.01</v>
       </c>
       <c r="F32" s="20">
         <v>0.01</v>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="20">
+        <v>0.01</v>
+      </c>
+      <c r="H32" s="25">
         <v>1</v>
       </c>
-      <c r="H32" s="23">
+      <c r="I32" s="23">
         <v>55</v>
-      </c>
-      <c r="I32" s="23">
-        <v>2</v>
       </c>
       <c r="J32" s="23">
         <v>2</v>
       </c>
       <c r="K32" s="23">
+        <v>2</v>
+      </c>
+      <c r="L32" s="23">
         <v>12</v>
       </c>
-      <c r="L32" s="23">
-        <v>0</v>
-      </c>
       <c r="M32" s="23">
         <v>0</v>
       </c>
       <c r="N32" s="23">
+        <v>0</v>
+      </c>
+      <c r="O32" s="23">
         <v>14</v>
-      </c>
-      <c r="O32" s="23">
-        <v>4</v>
       </c>
       <c r="P32" s="23">
         <v>4</v>
       </c>
-      <c r="Q32" s="24"/>
+      <c r="Q32" s="23">
+        <v>4</v>
+      </c>
       <c r="R32" s="24"/>
       <c r="S32" s="24"/>
       <c r="T32" s="24"/>
@@ -5379,54 +5462,57 @@
       <c r="Z32" s="24"/>
       <c r="AA32" s="24"/>
       <c r="AB32" s="24"/>
+      <c r="AC32" s="24"/>
     </row>
-    <row r="33" spans="1:28">
+    <row r="33" spans="1:29">
       <c r="B33" s="22" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="20">
+        <v>59</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="20">
         <v>0.98</v>
       </c>
-      <c r="E33" s="20">
-        <v>0</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G33" s="25">
+      <c r="F33" s="20">
+        <v>0</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H33" s="25">
         <v>2.576</v>
       </c>
-      <c r="H33" s="23">
+      <c r="I33" s="23">
         <v>66</v>
-      </c>
-      <c r="I33" s="23">
-        <v>2</v>
       </c>
       <c r="J33" s="23">
         <v>2</v>
       </c>
       <c r="K33" s="23">
+        <v>2</v>
+      </c>
+      <c r="L33" s="23">
         <v>11</v>
       </c>
-      <c r="L33" s="23">
-        <v>0</v>
-      </c>
       <c r="M33" s="23">
         <v>0</v>
       </c>
       <c r="N33" s="23">
+        <v>0</v>
+      </c>
+      <c r="O33" s="23">
         <v>14</v>
-      </c>
-      <c r="O33" s="23">
-        <v>4.4</v>
       </c>
       <c r="P33" s="23">
         <v>4.4</v>
       </c>
-      <c r="Q33" s="24"/>
+      <c r="Q33" s="23">
+        <v>4.4</v>
+      </c>
       <c r="R33" s="24"/>
       <c r="S33" s="24"/>
       <c r="T33" s="24"/>
@@ -5438,54 +5524,57 @@
       <c r="Z33" s="24"/>
       <c r="AA33" s="24"/>
       <c r="AB33" s="24"/>
+      <c r="AC33" s="24"/>
     </row>
-    <row r="34" spans="1:28">
+    <row r="34" spans="1:29">
       <c r="B34" s="22" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34" s="20">
+        <v>60</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="20">
         <v>0.72</v>
       </c>
-      <c r="E34" s="20">
+      <c r="F34" s="20">
         <v>0.017</v>
       </c>
-      <c r="F34" s="20">
+      <c r="G34" s="20">
         <v>0.009</v>
       </c>
-      <c r="G34" s="11">
+      <c r="H34" s="11">
         <v>1.645</v>
       </c>
-      <c r="H34" s="23">
+      <c r="I34" s="23">
         <v>66</v>
-      </c>
-      <c r="I34" s="23">
-        <v>2</v>
       </c>
       <c r="J34" s="23">
         <v>2</v>
       </c>
       <c r="K34" s="23">
+        <v>2</v>
+      </c>
+      <c r="L34" s="23">
         <v>12.5</v>
       </c>
-      <c r="L34" s="23">
-        <v>0</v>
-      </c>
       <c r="M34" s="23">
         <v>0</v>
       </c>
       <c r="N34" s="23">
+        <v>0</v>
+      </c>
+      <c r="O34" s="23">
         <v>14</v>
-      </c>
-      <c r="O34" s="23">
-        <v>4</v>
       </c>
       <c r="P34" s="23">
         <v>4</v>
       </c>
-      <c r="Q34" s="24"/>
+      <c r="Q34" s="23">
+        <v>4</v>
+      </c>
       <c r="R34" s="24"/>
       <c r="S34" s="24"/>
       <c r="T34" s="24"/>
@@ -5497,1715 +5586,1473 @@
       <c r="Z34" s="24"/>
       <c r="AA34" s="24"/>
       <c r="AB34" s="24"/>
+      <c r="AC34" s="24"/>
     </row>
-    <row r="35" spans="1:28">
+    <row r="35" spans="1:29">
       <c r="A35" s="3">
         <v>8</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D35" s="20">
-        <v>0.555</v>
+        <v>50</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="E35" s="20">
-        <v>0.265</v>
+        <v>0.49</v>
       </c>
       <c r="F35" s="20">
-        <v>0.265</v>
-      </c>
-      <c r="G35" s="26" t="s">
-        <v>35</v>
+        <v>0.2</v>
+      </c>
+      <c r="G35" s="20">
+        <v>0.13</v>
       </c>
       <c r="H35" s="11">
+        <v>1.645</v>
+      </c>
+      <c r="I35" s="11">
         <v>74.7</v>
-      </c>
-      <c r="I35" s="11">
-        <v>3.8</v>
       </c>
       <c r="J35" s="11">
         <v>3.8</v>
       </c>
-      <c r="K35" s="23">
+      <c r="K35" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="L35" s="23">
+        <v>4.38</v>
+      </c>
+      <c r="M35" s="23">
+        <v>0.41</v>
+      </c>
+      <c r="N35" s="23">
+        <v>0.58</v>
+      </c>
+      <c r="O35" s="23">
         <v>9.1</v>
       </c>
-      <c r="L35" s="23">
+      <c r="P35" s="23">
         <v>0.61</v>
       </c>
-      <c r="M35" s="23">
+      <c r="Q35" s="23">
         <v>0.61</v>
       </c>
-      <c r="N35" s="23">
-        <v>4.38</v>
-      </c>
-      <c r="O35" s="23">
-        <v>0.41</v>
-      </c>
-      <c r="P35" s="23">
-        <v>0.58</v>
-      </c>
-      <c r="Q35" s="24"/>
     </row>
-    <row r="36" spans="1:28">
+    <row r="36" spans="1:29">
       <c r="B36" s="22" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D36" s="20">
-        <v>0.94</v>
-      </c>
-      <c r="E36" s="20">
-        <v>0.05</v>
+        <v>34</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="5">
+        <v>0.76</v>
       </c>
       <c r="F36" s="20">
-        <v>0.05</v>
-      </c>
-      <c r="G36" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="I36" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K36" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L36" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M36" s="23" t="s">
-        <v>35</v>
+        <v>0.01</v>
+      </c>
+      <c r="G36" s="20">
+        <v>0.01</v>
+      </c>
+      <c r="H36" s="11">
+        <v>1</v>
+      </c>
+      <c r="I36" s="11">
+        <v>50</v>
+      </c>
+      <c r="J36" s="11">
+        <v>0</v>
+      </c>
+      <c r="K36" s="11">
+        <v>15</v>
+      </c>
+      <c r="L36" s="23">
+        <v>5.5</v>
+      </c>
+      <c r="M36" s="23">
+        <v>2.5</v>
       </c>
       <c r="N36" s="23">
-        <v>9.6</v>
+        <v>2.5</v>
       </c>
       <c r="O36" s="23">
-        <v>1.2</v>
+        <v>11</v>
       </c>
       <c r="P36" s="23">
-        <v>1.2</v>
+        <v>1</v>
+      </c>
+      <c r="Q36" s="23">
+        <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:28">
+    <row r="37" spans="1:29">
       <c r="B37" s="22" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D37" s="20">
-        <v>0.34</v>
+        <v>62</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="E37" s="20">
-        <v>0.01</v>
+        <v>0.72</v>
       </c>
       <c r="F37" s="20">
         <v>0.01</v>
       </c>
-      <c r="G37" s="11">
+      <c r="G37" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="H37" s="11">
+        <v>1.645</v>
+      </c>
+      <c r="I37" s="11">
+        <v>42</v>
+      </c>
+      <c r="J37" s="11">
+        <v>13</v>
+      </c>
+      <c r="K37" s="23">
+        <v>3</v>
+      </c>
+      <c r="L37" s="23">
+        <v>6.351</v>
+      </c>
+      <c r="M37" s="23">
+        <v>0.008</v>
+      </c>
+      <c r="N37" s="23">
+        <v>0.008</v>
+      </c>
+      <c r="O37" s="23">
+        <v>10</v>
+      </c>
+      <c r="P37" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29">
+      <c r="A38" s="3">
+        <v>9</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" s="20">
+        <v>0.94</v>
+      </c>
+      <c r="F38" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="G38" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="H38" s="11">
+        <v>1.645</v>
+      </c>
+      <c r="I38" s="20">
+        <v>32</v>
+      </c>
+      <c r="J38" s="20">
+        <v>0</v>
+      </c>
+      <c r="K38" s="20">
+        <v>0</v>
+      </c>
+      <c r="L38" s="20">
+        <v>2.96</v>
+      </c>
+      <c r="M38" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="N38" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="O38" s="5">
+        <v>8.48</v>
+      </c>
+      <c r="P38" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29">
+      <c r="B39" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="20">
+        <v>-0.396</v>
+      </c>
+      <c r="F39" s="20">
+        <v>0.432</v>
+      </c>
+      <c r="G39" s="20">
+        <v>0.661</v>
+      </c>
+      <c r="H39" s="20">
         <v>1</v>
       </c>
-      <c r="H37" s="11">
-        <v>74.7</v>
-      </c>
-      <c r="I37" s="11">
-        <v>3.8</v>
-      </c>
-      <c r="J37" s="11">
-        <v>3.8</v>
-      </c>
-      <c r="K37" s="23">
-        <v>4.38</v>
-      </c>
-      <c r="L37" s="23">
-        <v>0.41</v>
-      </c>
-      <c r="M37" s="23">
-        <v>0.58</v>
-      </c>
-      <c r="N37" s="23">
-        <v>9.1</v>
-      </c>
-      <c r="O37" s="23">
-        <v>0.61</v>
-      </c>
-      <c r="P37" s="23">
-        <v>0.61</v>
+      <c r="I39" s="20">
+        <v>61.85</v>
+      </c>
+      <c r="J39" s="20">
+        <v>3.19</v>
+      </c>
+      <c r="K39" s="20">
+        <v>3.07</v>
+      </c>
+      <c r="L39" s="20">
+        <v>2.98</v>
+      </c>
+      <c r="M39" s="20">
+        <v>0.47</v>
+      </c>
+      <c r="N39" s="20">
+        <v>0.53</v>
+      </c>
+      <c r="O39" s="5">
+        <v>8.41</v>
+      </c>
+      <c r="P39" s="5">
+        <v>0.64</v>
+      </c>
+      <c r="Q39" s="5">
+        <v>0.77</v>
       </c>
     </row>
-    <row r="38" spans="1:28">
-      <c r="B38" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" s="20">
-        <v>0.49</v>
-      </c>
-      <c r="E38" s="20">
-        <v>0.2</v>
-      </c>
-      <c r="F38" s="20">
-        <v>0.13</v>
-      </c>
-      <c r="G38" s="11">
+    <row r="40" spans="1:29">
+      <c r="B40" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="5">
+        <v>-0.141</v>
+      </c>
+      <c r="F40" s="20">
+        <v>0.564</v>
+      </c>
+      <c r="G40" s="20">
+        <v>0.492</v>
+      </c>
+      <c r="H40" s="20">
+        <v>1</v>
+      </c>
+      <c r="I40" s="20">
+        <v>62.43</v>
+      </c>
+      <c r="J40" s="20">
+        <v>2.45</v>
+      </c>
+      <c r="K40" s="20">
+        <v>2.45</v>
+      </c>
+      <c r="L40" s="20">
+        <v>2.94</v>
+      </c>
+      <c r="M40" s="20">
+        <v>0.43</v>
+      </c>
+      <c r="N40" s="20">
+        <v>0.38</v>
+      </c>
+      <c r="O40" s="20">
+        <v>8.4</v>
+      </c>
+      <c r="P40" s="20">
+        <v>0.74</v>
+      </c>
+      <c r="Q40" s="20">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29">
+      <c r="B41" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="5">
+        <v>0.77</v>
+      </c>
+      <c r="F41" s="10">
+        <v>0.21</v>
+      </c>
+      <c r="G41" s="10">
+        <v>0.21</v>
+      </c>
+      <c r="H41" s="11">
         <v>1.645</v>
       </c>
-      <c r="H38" s="11">
-        <v>74.7</v>
-      </c>
-      <c r="I38" s="11">
-        <v>3.8</v>
-      </c>
-      <c r="J38" s="11">
-        <v>3.8</v>
-      </c>
-      <c r="K38" s="23">
-        <v>4.38</v>
-      </c>
-      <c r="L38" s="23">
-        <v>0.41</v>
-      </c>
-      <c r="M38" s="23">
-        <v>0.58</v>
-      </c>
-      <c r="N38" s="23">
-        <v>9.1</v>
-      </c>
-      <c r="O38" s="23">
-        <v>0.61</v>
-      </c>
-      <c r="P38" s="23">
-        <v>0.61</v>
+      <c r="I41" s="20">
+        <v>64</v>
+      </c>
+      <c r="J41" s="20">
+        <v>5</v>
+      </c>
+      <c r="K41" s="20">
+        <v>5</v>
+      </c>
+      <c r="L41" s="20">
+        <v>2.96</v>
+      </c>
+      <c r="M41" s="20">
+        <v>0.33</v>
+      </c>
+      <c r="N41" s="20">
+        <v>0.33</v>
+      </c>
+      <c r="O41" s="20">
+        <v>7.5</v>
+      </c>
+      <c r="P41" s="20">
+        <v>2.5</v>
+      </c>
+      <c r="Q41" s="20">
+        <v>2.5</v>
       </c>
     </row>
-    <row r="39" spans="1:28">
-      <c r="B39" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D39" s="20">
-        <v>0.725</v>
-      </c>
-      <c r="E39" s="20">
-        <v>0.043</v>
-      </c>
-      <c r="F39" s="20">
-        <v>0.043</v>
-      </c>
-      <c r="G39" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="H39" s="11">
-        <v>74.7</v>
-      </c>
-      <c r="I39" s="11">
-        <v>3.8</v>
-      </c>
-      <c r="J39" s="11">
-        <v>3.8</v>
-      </c>
-      <c r="K39" s="23">
-        <v>4.38</v>
-      </c>
-      <c r="L39" s="23">
-        <v>0.41</v>
-      </c>
-      <c r="M39" s="23">
-        <v>0.58</v>
-      </c>
-      <c r="N39" s="23">
-        <v>9.5</v>
-      </c>
-      <c r="O39" s="23">
-        <v>1.5</v>
-      </c>
-      <c r="P39" s="23">
-        <v>1.5</v>
+    <row r="42" spans="1:29">
+      <c r="B42" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="5">
+        <v>0.988</v>
+      </c>
+      <c r="F42" s="20">
+        <v>0.028</v>
+      </c>
+      <c r="G42" s="20">
+        <v>0.006</v>
+      </c>
+      <c r="H42" s="20">
+        <v>1</v>
+      </c>
+      <c r="I42" s="20">
+        <v>64</v>
+      </c>
+      <c r="J42" s="20">
+        <v>4</v>
+      </c>
+      <c r="K42" s="20">
+        <v>3</v>
+      </c>
+      <c r="L42" s="20">
+        <v>2.96</v>
+      </c>
+      <c r="M42" s="20">
+        <v>0.33</v>
+      </c>
+      <c r="N42" s="20">
+        <v>0.33</v>
+      </c>
+      <c r="O42" s="20">
+        <v>8.48</v>
+      </c>
+      <c r="P42" s="20">
+        <v>0.79</v>
+      </c>
+      <c r="Q42" s="20">
+        <v>0.79</v>
       </c>
     </row>
-    <row r="40" spans="1:28">
-      <c r="B40" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D40" s="5">
-        <v>0.76</v>
-      </c>
-      <c r="E40" s="20">
-        <v>0.01</v>
-      </c>
-      <c r="F40" s="20">
-        <v>0.01</v>
-      </c>
-      <c r="G40" s="11">
+    <row r="43" spans="1:29">
+      <c r="B43" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="20">
+        <v>0.14</v>
+      </c>
+      <c r="F43" s="20">
+        <v>0.09</v>
+      </c>
+      <c r="G43" s="20">
+        <v>0.09</v>
+      </c>
+      <c r="H43" s="20">
         <v>1</v>
       </c>
-      <c r="H40" s="11">
-        <v>50</v>
-      </c>
-      <c r="I40" s="11">
-        <v>0</v>
-      </c>
-      <c r="J40" s="11">
-        <v>15</v>
-      </c>
-      <c r="K40" s="23">
-        <v>5.5</v>
-      </c>
-      <c r="L40" s="23">
-        <v>2.5</v>
-      </c>
-      <c r="M40" s="23">
-        <v>2.5</v>
-      </c>
-      <c r="N40" s="23">
-        <v>11</v>
-      </c>
-      <c r="O40" s="23">
-        <v>1</v>
-      </c>
-      <c r="P40" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:28">
-      <c r="B41" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" s="5">
-        <v>0.265</v>
-      </c>
-      <c r="E41" s="20">
-        <v>0.155</v>
-      </c>
-      <c r="F41" s="20">
-        <v>0.155</v>
-      </c>
-      <c r="G41" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="H41" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="I41" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="J41" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="K41" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="L41" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="M41" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="N41" s="23">
-        <v>9.6</v>
-      </c>
-      <c r="O41" s="23">
-        <v>1.2</v>
-      </c>
-      <c r="P41" s="23">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:28">
-      <c r="B42" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C42" s="4" t="s">
+      <c r="I43" s="20">
         <v>63</v>
-      </c>
-      <c r="D42" s="20">
-        <v>0.72</v>
-      </c>
-      <c r="E42" s="20">
-        <v>0.01</v>
-      </c>
-      <c r="F42" s="20">
-        <v>0.15</v>
-      </c>
-      <c r="G42" s="11">
-        <v>1.645</v>
-      </c>
-      <c r="H42" s="11">
-        <v>42</v>
-      </c>
-      <c r="I42" s="11">
-        <v>13</v>
-      </c>
-      <c r="J42" s="23">
-        <v>3</v>
-      </c>
-      <c r="K42" s="23">
-        <v>6.351</v>
-      </c>
-      <c r="L42" s="23">
-        <v>0.008</v>
-      </c>
-      <c r="M42" s="23">
-        <v>0.008</v>
-      </c>
-      <c r="N42" s="23">
-        <v>10</v>
-      </c>
-      <c r="O42" s="23">
-        <v>0</v>
-      </c>
-      <c r="P42" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:28">
-      <c r="A43" s="3">
-        <v>9</v>
-      </c>
-      <c r="B43" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D43" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F43" s="20">
-        <v>0</v>
-      </c>
-      <c r="G43" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="H43" s="20">
-        <v>63</v>
-      </c>
-      <c r="I43" s="20">
-        <v>3</v>
       </c>
       <c r="J43" s="20">
         <v>3</v>
       </c>
       <c r="K43" s="20">
+        <v>3</v>
+      </c>
+      <c r="L43" s="20">
         <v>2.96</v>
-      </c>
-      <c r="L43" s="20">
-        <v>0.33</v>
       </c>
       <c r="M43" s="20">
         <v>0.33</v>
       </c>
-      <c r="N43" s="5">
+      <c r="N43" s="20">
+        <v>0.33</v>
+      </c>
+      <c r="O43" s="20">
         <v>8.48</v>
       </c>
-      <c r="O43" s="5">
+      <c r="P43" s="20">
         <v>0.72</v>
       </c>
-      <c r="P43" s="5">
+      <c r="Q43" s="20">
         <v>0.79</v>
       </c>
     </row>
-    <row r="44" spans="1:28">
+    <row r="44" spans="1:29">
       <c r="B44" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="F44" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="G44" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="H44" s="20">
+        <v>1</v>
+      </c>
+      <c r="I44" s="20">
+        <v>63</v>
+      </c>
+      <c r="J44" s="20">
+        <v>3</v>
+      </c>
+      <c r="K44" s="20">
+        <v>3</v>
+      </c>
+      <c r="L44" s="20">
+        <v>2.96</v>
+      </c>
+      <c r="M44" s="20">
+        <v>0.33</v>
+      </c>
+      <c r="N44" s="20">
+        <v>0.33</v>
+      </c>
+      <c r="O44" s="20">
+        <v>8.48</v>
+      </c>
+      <c r="P44" s="20">
+        <v>0.72</v>
+      </c>
+      <c r="Q44" s="20">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29">
+      <c r="B45" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="20">
+        <v>0.998</v>
+      </c>
+      <c r="F45" s="21">
+        <v>0</v>
+      </c>
+      <c r="G45" s="21">
+        <v>0</v>
+      </c>
+      <c r="H45" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="I45" s="20">
+        <v>29.8</v>
+      </c>
+      <c r="J45" s="20">
+        <v>2.7</v>
+      </c>
+      <c r="K45" s="20">
+        <v>3</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M45" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N45" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="O45" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="P45" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q45" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29">
+      <c r="A46" s="3">
+        <v>10</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" s="5">
+        <v>0.79</v>
+      </c>
+      <c r="F46" s="21">
+        <v>0.13</v>
+      </c>
+      <c r="G46" s="21">
+        <v>0.13</v>
+      </c>
+      <c r="H46" s="11">
+        <v>1.645</v>
+      </c>
+      <c r="I46" s="20">
+        <v>29.3</v>
+      </c>
+      <c r="J46" s="20">
+        <v>0</v>
+      </c>
+      <c r="K46" s="20">
+        <v>0</v>
+      </c>
+      <c r="L46" s="20">
+        <v>3.39</v>
+      </c>
+      <c r="M46" s="20">
+        <v>0.34</v>
+      </c>
+      <c r="N46" s="20">
+        <v>0.34</v>
+      </c>
+      <c r="O46" s="5">
+        <v>11</v>
+      </c>
+      <c r="P46" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q46" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29">
+      <c r="B47" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="5">
+        <v>0.977</v>
+      </c>
+      <c r="F47" s="5">
+        <v>0.015</v>
+      </c>
+      <c r="G47" s="5">
+        <v>0.017</v>
+      </c>
+      <c r="H47" s="20">
+        <v>1</v>
+      </c>
+      <c r="I47" s="20">
+        <v>52</v>
+      </c>
+      <c r="J47" s="20">
+        <v>11</v>
+      </c>
+      <c r="K47" s="20">
+        <v>8</v>
+      </c>
+      <c r="L47" s="20">
+        <v>3.4</v>
+      </c>
+      <c r="M47" s="20">
+        <v>0.4</v>
+      </c>
+      <c r="N47" s="20">
+        <v>0.4</v>
+      </c>
+      <c r="O47" s="20">
+        <v>11</v>
+      </c>
+      <c r="P47" s="20">
+        <v>2</v>
+      </c>
+      <c r="Q47" s="20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29">
+      <c r="B48" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="20">
+        <v>0.41</v>
+      </c>
+      <c r="F48" s="20">
+        <v>0.03</v>
+      </c>
+      <c r="G48" s="20">
+        <v>0.03</v>
+      </c>
+      <c r="H48" s="20">
+        <v>1</v>
+      </c>
+      <c r="I48" s="20">
+        <v>29.2</v>
+      </c>
+      <c r="J48" s="20">
+        <v>0</v>
+      </c>
+      <c r="K48" s="20">
+        <v>0</v>
+      </c>
+      <c r="L48" s="20">
+        <v>3.39</v>
+      </c>
+      <c r="M48" s="20">
+        <v>0</v>
+      </c>
+      <c r="N48" s="20">
+        <v>0</v>
+      </c>
+      <c r="O48" s="20">
+        <v>11</v>
+      </c>
+      <c r="P48" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="B49" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="5">
+        <v>0.82</v>
+      </c>
+      <c r="F49" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="G49" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="H49" s="11">
+        <v>1.645</v>
+      </c>
+      <c r="I49" s="20">
+        <v>20.1</v>
+      </c>
+      <c r="J49" s="20">
+        <v>1.1</v>
+      </c>
+      <c r="K49" s="20">
+        <v>1.1</v>
+      </c>
+      <c r="L49" s="20">
+        <v>2.2</v>
+      </c>
+      <c r="M49" s="20">
+        <v>0.6</v>
+      </c>
+      <c r="N49" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="O49" s="5">
+        <v>8</v>
+      </c>
+      <c r="P49" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17">
+      <c r="B50" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="5">
+        <v>0.97</v>
+      </c>
+      <c r="F50" s="5">
+        <v>0</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H50" s="11">
+        <v>1.645</v>
+      </c>
+      <c r="I50" s="20">
+        <v>32.9</v>
+      </c>
+      <c r="J50" s="20">
+        <v>0.6</v>
+      </c>
+      <c r="K50" s="20">
+        <v>4.1</v>
+      </c>
+      <c r="L50" s="20">
+        <v>3.39</v>
+      </c>
+      <c r="M50" s="20">
+        <v>0</v>
+      </c>
+      <c r="N50" s="20">
+        <v>0</v>
+      </c>
+      <c r="O50" s="20">
+        <v>11</v>
+      </c>
+      <c r="P50" s="20">
+        <v>2</v>
+      </c>
+      <c r="Q50" s="20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17">
+      <c r="B51" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="F51" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="G51" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="H51" s="11">
+        <v>1.645</v>
+      </c>
+      <c r="I51" s="20">
+        <v>36.5</v>
+      </c>
+      <c r="J51" s="20">
+        <v>1</v>
+      </c>
+      <c r="K51" s="20">
+        <v>1</v>
+      </c>
+      <c r="L51" s="20">
+        <v>2.2</v>
+      </c>
+      <c r="M51" s="20">
+        <v>0</v>
+      </c>
+      <c r="N51" s="20">
+        <v>0</v>
+      </c>
+      <c r="O51" s="20">
+        <v>8.7</v>
+      </c>
+      <c r="P51" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="Q51" s="20">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17">
+      <c r="B52" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="F52" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="G52" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="H52" s="11">
+        <v>1.645</v>
+      </c>
+      <c r="I52" s="20">
+        <v>29.2</v>
+      </c>
+      <c r="J52" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="K52" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="L52" s="20">
+        <v>3.39</v>
+      </c>
+      <c r="M52" s="20">
+        <v>0</v>
+      </c>
+      <c r="N52" s="20">
+        <v>0</v>
+      </c>
+      <c r="O52" s="20">
+        <v>11</v>
+      </c>
+      <c r="P52" s="20">
+        <v>2</v>
+      </c>
+      <c r="Q52" s="20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17">
+      <c r="A53" s="3">
+        <v>11</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="F53" s="21">
+        <v>0</v>
+      </c>
+      <c r="G53" s="21">
+        <v>0</v>
+      </c>
+      <c r="H53" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J53" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K53" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M53" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N53" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="O53" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q53" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17">
+      <c r="B54" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="20">
+        <v>0.86</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G54" s="20">
+        <v>0</v>
+      </c>
+      <c r="H54" s="20">
+        <v>3.29</v>
+      </c>
+      <c r="I54" s="20">
+        <v>17</v>
+      </c>
+      <c r="J54" s="20">
+        <v>0</v>
+      </c>
+      <c r="K54" s="20">
+        <v>0</v>
+      </c>
+      <c r="L54" s="20">
+        <v>8.7</v>
+      </c>
+      <c r="M54" s="20">
+        <v>0</v>
+      </c>
+      <c r="N54" s="20">
+        <v>0</v>
+      </c>
+      <c r="O54" s="20">
+        <v>5.1</v>
+      </c>
+      <c r="P54" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17">
+      <c r="B55" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="F55" s="5">
+        <v>0</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H55" s="11">
+        <v>1.645</v>
+      </c>
+      <c r="I55" s="20">
+        <v>46.1</v>
+      </c>
+      <c r="J55" s="20">
+        <v>5.3</v>
+      </c>
+      <c r="K55" s="20">
+        <v>4</v>
+      </c>
+      <c r="L55" s="21">
+        <v>10</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N55" s="21">
+        <v>0</v>
+      </c>
+      <c r="O55" s="20">
+        <v>8.5</v>
+      </c>
+      <c r="P55" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="Q55" s="20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17">
+      <c r="B56" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="5">
+        <v>0.97</v>
+      </c>
+      <c r="F56" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="G56" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="H56" s="20">
+        <v>1</v>
+      </c>
+      <c r="I56" s="20">
+        <v>62</v>
+      </c>
+      <c r="J56" s="20">
+        <v>4</v>
+      </c>
+      <c r="K56" s="20">
+        <v>3</v>
+      </c>
+      <c r="L56" s="20">
+        <v>10</v>
+      </c>
+      <c r="M56" s="20">
+        <v>5</v>
+      </c>
+      <c r="N56" s="20">
+        <v>5</v>
+      </c>
+      <c r="O56" s="20">
+        <v>8</v>
+      </c>
+      <c r="P56" s="20">
+        <v>4</v>
+      </c>
+      <c r="Q56" s="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17">
+      <c r="B57" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E57" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G57" s="5">
+        <v>0</v>
+      </c>
+      <c r="H57" s="11">
+        <v>1.645</v>
+      </c>
+      <c r="I57" s="20">
         <v>64</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D44" s="20">
+      <c r="J57" s="20">
+        <v>6</v>
+      </c>
+      <c r="K57" s="20">
+        <v>6</v>
+      </c>
+      <c r="L57" s="20">
+        <v>8.7</v>
+      </c>
+      <c r="M57" s="20">
+        <v>2.3</v>
+      </c>
+      <c r="N57" s="20">
+        <v>2.3</v>
+      </c>
+      <c r="O57" s="20">
+        <v>5.1</v>
+      </c>
+      <c r="P57" s="20">
+        <v>1.6</v>
+      </c>
+      <c r="Q57" s="20">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17">
+      <c r="A58" s="3">
+        <v>12</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" s="20">
+        <v>0.655</v>
+      </c>
+      <c r="F58" s="21">
+        <v>0.155</v>
+      </c>
+      <c r="G58" s="21">
+        <v>0.155</v>
+      </c>
+      <c r="H58" s="11">
+        <v>1.645</v>
+      </c>
+      <c r="I58" s="20">
+        <v>25.5</v>
+      </c>
+      <c r="J58" s="20">
+        <v>15.5</v>
+      </c>
+      <c r="K58" s="20">
+        <v>15.5</v>
+      </c>
+      <c r="L58" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M58" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N58" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="O58" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="P58" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q58" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17">
+      <c r="B59" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" s="5">
+        <v>0.84</v>
+      </c>
+      <c r="F59" s="5">
+        <v>0.26</v>
+      </c>
+      <c r="G59" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="H59" s="11">
+        <v>1.645</v>
+      </c>
+      <c r="I59" s="20">
+        <v>21.1</v>
+      </c>
+      <c r="J59" s="20">
+        <v>3.6</v>
+      </c>
+      <c r="K59" s="20">
+        <v>4.5</v>
+      </c>
+      <c r="L59" s="20">
+        <v>5.8</v>
+      </c>
+      <c r="M59" s="20">
+        <v>2.5</v>
+      </c>
+      <c r="N59" s="20">
+        <v>2.5</v>
+      </c>
+      <c r="O59" s="20">
+        <v>8.07</v>
+      </c>
+      <c r="P59" s="20">
+        <v>3.69</v>
+      </c>
+      <c r="Q59" s="20">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17">
+      <c r="B60" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="20">
+        <v>0.7</v>
+      </c>
+      <c r="F60" s="21">
+        <v>0.17</v>
+      </c>
+      <c r="G60" s="21">
+        <v>0.17</v>
+      </c>
+      <c r="H60" s="20">
+        <v>1</v>
+      </c>
+      <c r="I60" s="20">
+        <v>46</v>
+      </c>
+      <c r="J60" s="20">
+        <v>15</v>
+      </c>
+      <c r="K60" s="20">
+        <v>15</v>
+      </c>
+      <c r="L60" s="20">
+        <v>10</v>
+      </c>
+      <c r="M60" s="20">
+        <v>0</v>
+      </c>
+      <c r="N60" s="20">
+        <v>0</v>
+      </c>
+      <c r="O60" s="20">
+        <v>9.65</v>
+      </c>
+      <c r="P60" s="20">
+        <v>0.45</v>
+      </c>
+      <c r="Q60" s="20">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17">
+      <c r="A61" s="3">
+        <v>13</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="20">
         <v>0.94</v>
       </c>
-      <c r="E44" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="F44" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="G44" s="11">
+      <c r="F61" s="20">
+        <v>0.03</v>
+      </c>
+      <c r="G61" s="20">
+        <v>0.06</v>
+      </c>
+      <c r="H61" s="20">
+        <v>2</v>
+      </c>
+      <c r="I61" s="20">
+        <v>28</v>
+      </c>
+      <c r="J61" s="20">
+        <v>4</v>
+      </c>
+      <c r="K61" s="20">
+        <v>3</v>
+      </c>
+      <c r="L61" s="5">
+        <v>8</v>
+      </c>
+      <c r="M61" s="5">
+        <v>0</v>
+      </c>
+      <c r="N61" s="5">
+        <v>0</v>
+      </c>
+      <c r="O61" s="20">
+        <v>2.5</v>
+      </c>
+      <c r="P61" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="B62" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="5">
+        <v>0.49</v>
+      </c>
+      <c r="F62" s="20">
+        <v>0.22</v>
+      </c>
+      <c r="G62" s="20">
+        <v>0.07</v>
+      </c>
+      <c r="H62" s="11">
         <v>1.645</v>
       </c>
-      <c r="H44" s="20">
-        <v>32</v>
-      </c>
-      <c r="I44" s="20">
-        <v>0</v>
-      </c>
-      <c r="J44" s="20">
-        <v>0</v>
-      </c>
-      <c r="K44" s="20">
-        <v>2.96</v>
-      </c>
-      <c r="L44" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="M44" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="N44" s="5">
-        <v>8.48</v>
-      </c>
-      <c r="O44" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="P44" s="5">
-        <v>0.79</v>
+      <c r="I62" s="20">
+        <v>21.2</v>
+      </c>
+      <c r="J62" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K62" s="20">
+        <v>0</v>
+      </c>
+      <c r="L62" s="27">
+        <v>8</v>
+      </c>
+      <c r="M62" s="27">
+        <v>0</v>
+      </c>
+      <c r="N62" s="27">
+        <v>0</v>
+      </c>
+      <c r="O62" s="20">
+        <v>10</v>
+      </c>
+      <c r="P62" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="20">
+        <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:28">
-      <c r="B45" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D45" s="20">
-        <v>-0.396</v>
-      </c>
-      <c r="E45" s="20">
-        <v>0.432</v>
-      </c>
-      <c r="F45" s="20">
-        <v>0.661</v>
-      </c>
-      <c r="G45" s="20">
+    <row r="63" spans="1:17">
+      <c r="B63" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" s="20">
+        <v>0.665</v>
+      </c>
+      <c r="F63" s="21">
+        <v>0.035</v>
+      </c>
+      <c r="G63" s="21">
+        <v>0.035</v>
+      </c>
+      <c r="H63" s="20">
         <v>1</v>
       </c>
-      <c r="H45" s="20">
-        <v>61.85</v>
-      </c>
-      <c r="I45" s="20">
-        <v>3.19</v>
-      </c>
-      <c r="J45" s="20">
-        <v>3.07</v>
-      </c>
-      <c r="K45" s="20">
-        <v>2.98</v>
-      </c>
-      <c r="L45" s="20">
-        <v>0.47</v>
-      </c>
-      <c r="M45" s="20">
-        <v>0.53</v>
-      </c>
-      <c r="N45" s="5">
-        <v>8.41</v>
-      </c>
-      <c r="O45" s="5">
-        <v>0.64</v>
-      </c>
-      <c r="P45" s="5">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="46" spans="1:28">
-      <c r="B46" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-0.141</v>
-      </c>
-      <c r="E46" s="20">
-        <v>0.564</v>
-      </c>
-      <c r="F46" s="20">
-        <v>0.492</v>
-      </c>
-      <c r="G46" s="20">
-        <v>1</v>
-      </c>
-      <c r="H46" s="20">
-        <v>62.43</v>
-      </c>
-      <c r="I46" s="20">
-        <v>2.45</v>
-      </c>
-      <c r="J46" s="20">
-        <v>2.45</v>
-      </c>
-      <c r="K46" s="20">
-        <v>2.94</v>
-      </c>
-      <c r="L46" s="20">
-        <v>0.43</v>
-      </c>
-      <c r="M46" s="20">
-        <v>0.38</v>
-      </c>
-      <c r="N46" s="20">
-        <v>8.4</v>
-      </c>
-      <c r="O46" s="20">
-        <v>0.74</v>
-      </c>
-      <c r="P46" s="20">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="47" spans="1:28">
-      <c r="B47" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D47" s="5">
-        <v>0.77</v>
-      </c>
-      <c r="E47" s="10">
-        <v>0.21</v>
-      </c>
-      <c r="F47" s="10">
-        <v>0.21</v>
-      </c>
-      <c r="G47" s="11">
-        <v>1.645</v>
-      </c>
-      <c r="H47" s="20">
-        <v>64</v>
-      </c>
-      <c r="I47" s="20">
-        <v>5</v>
-      </c>
-      <c r="J47" s="20">
-        <v>5</v>
-      </c>
-      <c r="K47" s="20">
-        <v>2.96</v>
-      </c>
-      <c r="L47" s="20">
-        <v>0.33</v>
-      </c>
-      <c r="M47" s="20">
-        <v>0.33</v>
-      </c>
-      <c r="N47" s="20">
-        <v>7.5</v>
-      </c>
-      <c r="O47" s="20">
+      <c r="I63" s="20">
+        <v>21.5</v>
+      </c>
+      <c r="J63" s="20">
         <v>2.5</v>
       </c>
-      <c r="P47" s="20">
+      <c r="K63" s="20">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="48" spans="1:28">
-      <c r="B48" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D48" s="5">
-        <v>0.988</v>
-      </c>
-      <c r="E48" s="20">
-        <v>0.028</v>
-      </c>
-      <c r="F48" s="20">
-        <v>0.006</v>
-      </c>
-      <c r="G48" s="20">
-        <v>1</v>
-      </c>
-      <c r="H48" s="20">
-        <v>64</v>
-      </c>
-      <c r="I48" s="20">
-        <v>4</v>
-      </c>
-      <c r="J48" s="20">
-        <v>3</v>
-      </c>
-      <c r="K48" s="20">
-        <v>2.96</v>
-      </c>
-      <c r="L48" s="20">
-        <v>0.33</v>
-      </c>
-      <c r="M48" s="20">
-        <v>0.33</v>
-      </c>
-      <c r="N48" s="20">
-        <v>8.48</v>
-      </c>
-      <c r="O48" s="20">
-        <v>0.79</v>
-      </c>
-      <c r="P48" s="20">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16">
-      <c r="B49" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D49" s="20">
-        <v>0.14</v>
-      </c>
-      <c r="E49" s="20">
-        <v>0.09</v>
-      </c>
-      <c r="F49" s="20">
-        <v>0.09</v>
-      </c>
-      <c r="G49" s="20">
-        <v>1</v>
-      </c>
-      <c r="H49" s="20">
-        <v>63</v>
-      </c>
-      <c r="I49" s="20">
-        <v>3</v>
-      </c>
-      <c r="J49" s="20">
-        <v>3</v>
-      </c>
-      <c r="K49" s="20">
-        <v>2.96</v>
-      </c>
-      <c r="L49" s="20">
-        <v>0.33</v>
-      </c>
-      <c r="M49" s="20">
-        <v>0.33</v>
-      </c>
-      <c r="N49" s="20">
-        <v>8.48</v>
-      </c>
-      <c r="O49" s="20">
-        <v>0.72</v>
-      </c>
-      <c r="P49" s="20">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16">
-      <c r="B50" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D50" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="E50" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="F50" s="20">
-        <v>0.2</v>
-      </c>
-      <c r="G50" s="20">
-        <v>1</v>
-      </c>
-      <c r="H50" s="20">
-        <v>63</v>
-      </c>
-      <c r="I50" s="20">
-        <v>3</v>
-      </c>
-      <c r="J50" s="20">
-        <v>3</v>
-      </c>
-      <c r="K50" s="20">
-        <v>2.96</v>
-      </c>
-      <c r="L50" s="20">
-        <v>0.33</v>
-      </c>
-      <c r="M50" s="20">
-        <v>0.33</v>
-      </c>
-      <c r="N50" s="20">
-        <v>8.48</v>
-      </c>
-      <c r="O50" s="20">
-        <v>0.72</v>
-      </c>
-      <c r="P50" s="20">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16">
-      <c r="B51" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D51" s="5">
-        <v>0.799</v>
-      </c>
-      <c r="E51" s="20">
-        <v>0.015</v>
-      </c>
-      <c r="F51" s="20">
-        <v>0.016</v>
-      </c>
-      <c r="G51" s="20">
-        <v>1</v>
-      </c>
-      <c r="H51" s="20">
-        <v>63</v>
-      </c>
-      <c r="I51" s="20">
-        <v>3</v>
-      </c>
-      <c r="J51" s="20">
-        <v>3</v>
-      </c>
-      <c r="K51" s="20">
-        <v>2.96</v>
-      </c>
-      <c r="L51" s="20">
-        <v>0.33</v>
-      </c>
-      <c r="M51" s="20">
-        <v>0.33</v>
-      </c>
-      <c r="N51" s="20">
-        <v>8.48</v>
-      </c>
-      <c r="O51" s="20">
-        <v>0.72</v>
-      </c>
-      <c r="P51" s="20">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16">
-      <c r="B52" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D52" s="20">
-        <v>0.998</v>
-      </c>
-      <c r="E52" s="21">
-        <v>0</v>
-      </c>
-      <c r="F52" s="21">
-        <v>0</v>
-      </c>
-      <c r="G52" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="H52" s="20">
-        <v>29.8</v>
-      </c>
-      <c r="I52" s="20">
-        <v>2.7</v>
-      </c>
-      <c r="J52" s="20">
-        <v>3</v>
-      </c>
-      <c r="K52" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="L52" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M52" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N52" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="O52" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="P52" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16">
-      <c r="A53" s="3">
-        <v>10</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D53" s="5">
-        <v>0.79</v>
-      </c>
-      <c r="E53" s="21">
-        <v>0.13</v>
-      </c>
-      <c r="F53" s="21">
-        <v>0.13</v>
-      </c>
-      <c r="G53" s="11">
-        <v>1.645</v>
-      </c>
-      <c r="H53" s="20">
-        <v>29.3</v>
-      </c>
-      <c r="I53" s="20">
-        <v>0</v>
-      </c>
-      <c r="J53" s="20">
-        <v>0</v>
-      </c>
-      <c r="K53" s="20">
-        <v>3.39</v>
-      </c>
-      <c r="L53" s="20">
-        <v>0.34</v>
-      </c>
-      <c r="M53" s="20">
-        <v>0.34</v>
-      </c>
-      <c r="N53" s="5">
-        <v>11</v>
-      </c>
-      <c r="O53" s="5">
-        <v>2</v>
-      </c>
-      <c r="P53" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16">
-      <c r="B54" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D54" s="5">
-        <v>0.977</v>
-      </c>
-      <c r="E54" s="5">
-        <v>0.015</v>
-      </c>
-      <c r="F54" s="5">
-        <v>0.017</v>
-      </c>
-      <c r="G54" s="20">
-        <v>1</v>
-      </c>
-      <c r="H54" s="20">
-        <v>52</v>
-      </c>
-      <c r="I54" s="20">
-        <v>11</v>
-      </c>
-      <c r="J54" s="20">
+      <c r="L63" s="27">
         <v>8</v>
       </c>
-      <c r="K54" s="20">
-        <v>3.4</v>
-      </c>
-      <c r="L54" s="20">
-        <v>0.4</v>
-      </c>
-      <c r="M54" s="20">
-        <v>0.4</v>
-      </c>
-      <c r="N54" s="20">
-        <v>11</v>
-      </c>
-      <c r="O54" s="20">
-        <v>2</v>
-      </c>
-      <c r="P54" s="20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16">
-      <c r="B55" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D55" s="20">
-        <v>0.41</v>
-      </c>
-      <c r="E55" s="20">
-        <v>0.03</v>
-      </c>
-      <c r="F55" s="20">
-        <v>0.03</v>
-      </c>
-      <c r="G55" s="20">
-        <v>1</v>
-      </c>
-      <c r="H55" s="20">
-        <v>29.2</v>
-      </c>
-      <c r="I55" s="20">
-        <v>0</v>
-      </c>
-      <c r="J55" s="20">
-        <v>0</v>
-      </c>
-      <c r="K55" s="20">
-        <v>3.39</v>
-      </c>
-      <c r="L55" s="20">
-        <v>0</v>
-      </c>
-      <c r="M55" s="20">
-        <v>0</v>
-      </c>
-      <c r="N55" s="20">
-        <v>11</v>
-      </c>
-      <c r="O55" s="20">
-        <v>0</v>
-      </c>
-      <c r="P55" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16">
-      <c r="B56" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D56" s="5">
-        <v>0.82</v>
-      </c>
-      <c r="E56" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="F56" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="G56" s="11">
-        <v>1.645</v>
-      </c>
-      <c r="H56" s="20">
-        <v>20.1</v>
-      </c>
-      <c r="I56" s="20">
-        <v>1.1</v>
-      </c>
-      <c r="J56" s="20">
-        <v>1.1</v>
-      </c>
-      <c r="K56" s="20">
+      <c r="M63" s="27">
+        <v>0</v>
+      </c>
+      <c r="N63" s="27">
+        <v>0</v>
+      </c>
+      <c r="O63" s="20">
+        <v>7.9</v>
+      </c>
+      <c r="P63" s="20">
         <v>2.2</v>
       </c>
-      <c r="L56" s="20">
-        <v>0.6</v>
-      </c>
-      <c r="M56" s="20">
-        <v>0.5</v>
-      </c>
-      <c r="N56" s="5">
-        <v>8</v>
-      </c>
-      <c r="O56" s="5">
-        <v>0</v>
-      </c>
-      <c r="P56" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16">
-      <c r="B57" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D57" s="5">
-        <v>0.97</v>
-      </c>
-      <c r="E57" s="5">
-        <v>0</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G57" s="11">
-        <v>1.645</v>
-      </c>
-      <c r="H57" s="20">
-        <v>32.9</v>
-      </c>
-      <c r="I57" s="20">
-        <v>0.6</v>
-      </c>
-      <c r="J57" s="20">
-        <v>4.1</v>
-      </c>
-      <c r="K57" s="20">
-        <v>3.39</v>
-      </c>
-      <c r="L57" s="20">
-        <v>0</v>
-      </c>
-      <c r="M57" s="20">
-        <v>0</v>
-      </c>
-      <c r="N57" s="20">
-        <v>11</v>
-      </c>
-      <c r="O57" s="20">
-        <v>2</v>
-      </c>
-      <c r="P57" s="20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16">
-      <c r="B58" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D58" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="E58" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="F58" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="G58" s="11">
-        <v>1.645</v>
-      </c>
-      <c r="H58" s="20">
-        <v>36.5</v>
-      </c>
-      <c r="I58" s="20">
-        <v>1</v>
-      </c>
-      <c r="J58" s="20">
-        <v>1</v>
-      </c>
-      <c r="K58" s="20">
-        <v>2.2</v>
-      </c>
-      <c r="L58" s="20">
-        <v>0</v>
-      </c>
-      <c r="M58" s="20">
-        <v>0</v>
-      </c>
-      <c r="N58" s="20">
-        <v>8.7</v>
-      </c>
-      <c r="O58" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="P58" s="20">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16">
-      <c r="B59" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D59" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="E59" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="F59" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="G59" s="11">
-        <v>1.645</v>
-      </c>
-      <c r="H59" s="20">
-        <v>29.2</v>
-      </c>
-      <c r="I59" s="20">
-        <v>0.5</v>
-      </c>
-      <c r="J59" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="K59" s="20">
-        <v>3.39</v>
-      </c>
-      <c r="L59" s="20">
-        <v>0</v>
-      </c>
-      <c r="M59" s="20">
-        <v>0</v>
-      </c>
-      <c r="N59" s="20">
-        <v>11</v>
-      </c>
-      <c r="O59" s="20">
-        <v>2</v>
-      </c>
-      <c r="P59" s="20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16">
-      <c r="A60" s="3">
-        <v>11</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" s="21">
-        <v>0.2</v>
-      </c>
-      <c r="E60" s="21">
-        <v>0</v>
-      </c>
-      <c r="F60" s="21">
-        <v>0</v>
-      </c>
-      <c r="G60" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="H60" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I60" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J60" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="K60" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="L60" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M60" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N60" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="O60" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="P60" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16">
-      <c r="B61" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D61" s="20">
-        <v>0.86</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F61" s="20">
-        <v>0</v>
-      </c>
-      <c r="G61" s="20">
-        <v>3.29</v>
-      </c>
-      <c r="H61" s="20">
-        <v>17</v>
-      </c>
-      <c r="I61" s="20">
-        <v>0</v>
-      </c>
-      <c r="J61" s="20">
-        <v>0</v>
-      </c>
-      <c r="K61" s="20">
-        <v>8.7</v>
-      </c>
-      <c r="L61" s="20">
-        <v>0</v>
-      </c>
-      <c r="M61" s="20">
-        <v>0</v>
-      </c>
-      <c r="N61" s="20">
-        <v>5.1</v>
-      </c>
-      <c r="O61" s="20">
-        <v>0</v>
-      </c>
-      <c r="P61" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16">
-      <c r="B62" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D62" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="E62" s="5">
-        <v>0</v>
-      </c>
-      <c r="F62" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G62" s="11">
-        <v>1.645</v>
-      </c>
-      <c r="H62" s="20">
-        <v>46.1</v>
-      </c>
-      <c r="I62" s="20">
-        <v>5.3</v>
-      </c>
-      <c r="J62" s="20">
-        <v>4</v>
-      </c>
-      <c r="K62" s="21">
-        <v>10</v>
-      </c>
-      <c r="L62" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M62" s="21">
-        <v>0</v>
-      </c>
-      <c r="N62" s="20">
-        <v>8.5</v>
-      </c>
-      <c r="O62" s="20">
-        <v>3.5</v>
-      </c>
-      <c r="P62" s="20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16">
-      <c r="B63" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D63" s="5">
-        <v>0.97</v>
-      </c>
-      <c r="E63" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="F63" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="G63" s="20">
-        <v>1</v>
-      </c>
-      <c r="H63" s="20">
-        <v>62</v>
-      </c>
-      <c r="I63" s="20">
-        <v>4</v>
-      </c>
-      <c r="J63" s="20">
-        <v>3</v>
-      </c>
-      <c r="K63" s="20">
-        <v>10</v>
-      </c>
-      <c r="L63" s="20">
-        <v>5</v>
-      </c>
-      <c r="M63" s="20">
-        <v>5</v>
-      </c>
-      <c r="N63" s="20">
-        <v>8</v>
-      </c>
-      <c r="O63" s="20">
-        <v>4</v>
-      </c>
-      <c r="P63" s="20">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16">
-      <c r="B64" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D64" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F64" s="5">
-        <v>0</v>
-      </c>
-      <c r="G64" s="11">
-        <v>1.645</v>
-      </c>
-      <c r="H64" s="20">
-        <v>64</v>
-      </c>
-      <c r="I64" s="20">
-        <v>6</v>
-      </c>
-      <c r="J64" s="20">
-        <v>6</v>
-      </c>
-      <c r="K64" s="20">
-        <v>8.7</v>
-      </c>
-      <c r="L64" s="20">
-        <v>2.3</v>
-      </c>
-      <c r="M64" s="20">
-        <v>2.3</v>
-      </c>
-      <c r="N64" s="20">
-        <v>5.1</v>
-      </c>
-      <c r="O64" s="20">
-        <v>1.6</v>
-      </c>
-      <c r="P64" s="20">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16">
-      <c r="A65" s="3">
-        <v>12</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D65" s="20">
-        <v>0.655</v>
-      </c>
-      <c r="E65" s="21">
-        <v>0.155</v>
-      </c>
-      <c r="F65" s="21">
-        <v>0.155</v>
-      </c>
-      <c r="G65" s="11">
-        <v>1.645</v>
-      </c>
-      <c r="H65" s="20">
-        <v>25.5</v>
-      </c>
-      <c r="I65" s="20">
-        <v>15.5</v>
-      </c>
-      <c r="J65" s="20">
-        <v>15.5</v>
-      </c>
-      <c r="K65" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="L65" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M65" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N65" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="O65" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16">
-      <c r="B66" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D66" s="5">
-        <v>0.84</v>
-      </c>
-      <c r="E66" s="5">
-        <v>0.26</v>
-      </c>
-      <c r="F66" s="5">
-        <v>0.17</v>
-      </c>
-      <c r="G66" s="11">
-        <v>1.645</v>
-      </c>
-      <c r="H66" s="20">
-        <v>21.1</v>
-      </c>
-      <c r="I66" s="20">
-        <v>3.6</v>
-      </c>
-      <c r="J66" s="20">
-        <v>4.5</v>
-      </c>
-      <c r="K66" s="20">
-        <v>5.8</v>
-      </c>
-      <c r="L66" s="20">
-        <v>2.5</v>
-      </c>
-      <c r="M66" s="20">
-        <v>2.5</v>
-      </c>
-      <c r="N66" s="20">
-        <v>8.07</v>
-      </c>
-      <c r="O66" s="20">
-        <v>3.69</v>
-      </c>
-      <c r="P66" s="20">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16">
-      <c r="B67" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D67" s="20">
-        <v>0.7</v>
-      </c>
-      <c r="E67" s="21">
-        <v>0.17</v>
-      </c>
-      <c r="F67" s="21">
-        <v>0.17</v>
-      </c>
-      <c r="G67" s="20">
-        <v>1</v>
-      </c>
-      <c r="H67" s="20">
-        <v>46</v>
-      </c>
-      <c r="I67" s="20">
-        <v>15</v>
-      </c>
-      <c r="J67" s="20">
-        <v>15</v>
-      </c>
-      <c r="K67" s="20">
-        <v>10</v>
-      </c>
-      <c r="L67" s="20">
-        <v>0</v>
-      </c>
-      <c r="M67" s="20">
-        <v>0</v>
-      </c>
-      <c r="N67" s="20">
-        <v>9.65</v>
-      </c>
-      <c r="O67" s="20">
-        <v>0.45</v>
-      </c>
-      <c r="P67" s="20">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16">
-      <c r="A68" s="3">
-        <v>13</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D68" s="20">
-        <v>0.94</v>
-      </c>
-      <c r="E68" s="20">
-        <v>0.03</v>
-      </c>
-      <c r="F68" s="20">
-        <v>0.06</v>
-      </c>
-      <c r="G68" s="20">
-        <v>2</v>
-      </c>
-      <c r="H68" s="20">
-        <v>28</v>
-      </c>
-      <c r="I68" s="20">
-        <v>4</v>
-      </c>
-      <c r="J68" s="20">
-        <v>3</v>
-      </c>
-      <c r="K68" s="5">
-        <v>8</v>
-      </c>
-      <c r="L68" s="5">
-        <v>0</v>
-      </c>
-      <c r="M68" s="5">
-        <v>0</v>
-      </c>
-      <c r="N68" s="20">
-        <v>2.5</v>
-      </c>
-      <c r="O68" s="20">
-        <v>0</v>
-      </c>
-      <c r="P68" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16">
-      <c r="B69" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D69" s="5">
-        <v>0.49</v>
-      </c>
-      <c r="E69" s="20">
-        <v>0.22</v>
-      </c>
-      <c r="F69" s="20">
-        <v>0.07</v>
-      </c>
-      <c r="G69" s="11">
-        <v>1.645</v>
-      </c>
-      <c r="H69" s="20">
-        <v>21.2</v>
-      </c>
-      <c r="I69" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J69" s="20">
-        <v>0</v>
-      </c>
-      <c r="K69" s="28">
-        <v>8</v>
-      </c>
-      <c r="L69" s="28">
-        <v>0</v>
-      </c>
-      <c r="M69" s="28">
-        <v>0</v>
-      </c>
-      <c r="N69" s="20">
-        <v>10</v>
-      </c>
-      <c r="O69" s="20">
-        <v>0</v>
-      </c>
-      <c r="P69" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16">
-      <c r="B70" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D70" s="20">
-        <v>0.665</v>
-      </c>
-      <c r="E70" s="21">
-        <v>0.035</v>
-      </c>
-      <c r="F70" s="21">
-        <v>0.035</v>
-      </c>
-      <c r="G70" s="20">
-        <v>1</v>
-      </c>
-      <c r="H70" s="20">
-        <v>21.5</v>
-      </c>
-      <c r="I70" s="20">
-        <v>2.5</v>
-      </c>
-      <c r="J70" s="20">
-        <v>2.5</v>
-      </c>
-      <c r="K70" s="28">
-        <v>8</v>
-      </c>
-      <c r="L70" s="28">
-        <v>0</v>
-      </c>
-      <c r="M70" s="28">
-        <v>0</v>
-      </c>
-      <c r="N70" s="20">
-        <v>7.9</v>
-      </c>
-      <c r="O70" s="20">
-        <v>2.2</v>
-      </c>
-      <c r="P70" s="20">
+      <c r="Q63" s="20">
         <v>2.2</v>
       </c>
     </row>

--- a/data/数据收集 表2 画图用.xlsx
+++ b/data/数据收集 表2 画图用.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="84">
   <si>
     <t>序号</t>
   </si>
@@ -146,16 +146,16 @@
     <t>Draghis 2020</t>
   </si>
   <si>
+    <t>GX 339-4</t>
+  </si>
+  <si>
+    <t>Zdziarski 2025</t>
+  </si>
+  <si>
+    <t>Zdziarski 2019</t>
+  </si>
+  <si>
     <t>NaN</t>
-  </si>
-  <si>
-    <t>GX 339-4</t>
-  </si>
-  <si>
-    <t>Zdziarski 2025</t>
-  </si>
-  <si>
-    <t>Zdziarski 2019</t>
   </si>
   <si>
     <t>García 2015</t>
@@ -3694,8 +3694,8 @@
       <c r="F17" s="11">
         <v>0</v>
       </c>
-      <c r="G17" s="10" t="s">
-        <v>39</v>
+      <c r="G17" s="10">
+        <v>0.022</v>
       </c>
       <c r="H17" s="11">
         <v>1.645</v>
@@ -3832,10 +3832,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>19</v>
@@ -3982,10 +3982,10 @@
     <row r="19" customFormat="1" spans="1:116">
       <c r="A19" s="3"/>
       <c r="B19" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>23</v>
@@ -3994,7 +3994,7 @@
         <v>0.8</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G19" s="10">
         <v>0</v>
@@ -4132,7 +4132,7 @@
     <row r="20" customFormat="1" spans="1:116">
       <c r="A20" s="3"/>
       <c r="B20" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>43</v>
@@ -4282,7 +4282,7 @@
     <row r="21" s="1" customFormat="1" spans="1:116">
       <c r="A21" s="3"/>
       <c r="B21" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>44</v>
@@ -4296,8 +4296,8 @@
       <c r="F21" s="10">
         <v>0</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>39</v>
+      <c r="G21" s="10">
+        <v>0.028</v>
       </c>
       <c r="H21" s="11">
         <v>1.645</v>
@@ -4432,7 +4432,7 @@
     <row r="22" customFormat="1" spans="1:116">
       <c r="A22" s="3"/>
       <c r="B22" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>45</v>
@@ -4477,7 +4477,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
@@ -4584,7 +4584,7 @@
         <v>46</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>47</v>
@@ -4598,8 +4598,8 @@
       <c r="F23" s="11">
         <v>0.05</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>39</v>
+      <c r="G23" s="10">
+        <v>0.148</v>
       </c>
       <c r="H23" s="11">
         <v>1</v>
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:116">
@@ -4974,7 +4974,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H28" s="11">
         <v>1.645</v>
@@ -5312,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H32" s="25">
         <v>2.576</v>
@@ -6044,8 +6044,8 @@
       <c r="F46" s="5">
         <v>0</v>
       </c>
-      <c r="G46" s="10" t="s">
-        <v>39</v>
+      <c r="G46" s="10">
+        <v>0.028</v>
       </c>
       <c r="H46" s="11">
         <v>1.645</v>
@@ -6195,7 +6195,7 @@
         <v>0.86</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G49" s="20">
         <v>0</v>
@@ -6247,8 +6247,8 @@
       <c r="F50" s="5">
         <v>0</v>
       </c>
-      <c r="G50" s="10" t="s">
-        <v>39</v>
+      <c r="G50" s="10">
+        <v>0.278</v>
       </c>
       <c r="H50" s="11">
         <v>1.645</v>
@@ -6266,7 +6266,7 @@
         <v>10</v>
       </c>
       <c r="M50" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N50" s="21">
         <v>0</v>
@@ -6344,8 +6344,8 @@
       <c r="E52" s="5">
         <v>0.25</v>
       </c>
-      <c r="F52" s="10" t="s">
-        <v>39</v>
+      <c r="F52" s="10">
+        <v>1.248</v>
       </c>
       <c r="G52" s="5">
         <v>0</v>
@@ -6416,22 +6416,22 @@
         <v>15.5</v>
       </c>
       <c r="L53" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M53" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q53" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:17">
@@ -6584,7 +6584,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:17">
@@ -6613,7 +6613,7 @@
         <v>21.2</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K57" s="20">
         <v>0</v>
